--- a/workspaces/btc_daily_14days/volatility/realized_vol_30.xlsx
+++ b/workspaces/btc_daily_14days/volatility/realized_vol_30.xlsx
@@ -575,46 +575,46 @@
         <v>137</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>3.710941241833815</v>
+        <v>3.69819869816228</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>8.670944570632898</v>
+        <v>8.641904181726154</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>14.12056125095725</v>
+        <v>14.07309042107627</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>10.60213608073148</v>
+        <v>10.56634301493975</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>11.52724615288066</v>
+        <v>11.48845021751178</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>8.173792344260512</v>
+        <v>8.146033441547473</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>13.93931162613314</v>
+        <v>13.89269916891332</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>14.20626653621515</v>
+        <v>14.15849201283572</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>14.14862163152608</v>
+        <v>14.10136707864242</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>12.56882216379937</v>
+        <v>12.52645307014659</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>10.90323220332017</v>
+        <v>10.86637742706458</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>8.744714541677226</v>
+        <v>8.714897232551863</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>8.325591224692367</v>
+        <v>8.297033122871433</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>8.578448202560395</v>
+        <v>8.548951232210428</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>205</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>3.116317777351007</v>
+        <v>3.104478086450818</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.04145751569719636</v>
+        <v>0.03979370475792621</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-1.329450099135769</v>
+        <v>-1.327492515702311</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-1.199358642117801</v>
+        <v>-1.197352992274759</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.7618380025564733</v>
+        <v>-0.7614130854154055</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.02428401560811011</v>
+        <v>0.02234842308095608</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.06019998830549866</v>
+        <v>-0.06235402768893294</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-2.482794835946045</v>
+        <v>-2.476856130184366</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-2.055757808300783</v>
+        <v>-2.050938498899882</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-1.441243512428123</v>
+        <v>-1.438728904939381</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-2.136026116460677</v>
+        <v>-2.130871247554325</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.6343451888443212</v>
+        <v>-0.6342481052585072</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.4122477180051405</v>
+        <v>0.4086177540060874</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>1.642284031260957</v>
+        <v>1.634228070380495</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>200</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>3.006561679790138</v>
+        <v>2.993769161295631</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.8953722754424192</v>
+        <v>0.8903775634259432</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-1.500312979937462</v>
+        <v>-1.497502768854474</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-1.870713125834016</v>
+        <v>-1.866008778261218</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-2.41005947646881</v>
+        <v>-2.403524525210685</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-1.612091568333852</v>
+        <v>-1.608231130417693</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-2.698710806498894</v>
+        <v>-2.691408479634362</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-4.670419959569422</v>
+        <v>-4.65575585000586</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-3.229485538823972</v>
+        <v>-3.219797691713801</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-5.08486585341673</v>
+        <v>-5.068663691058042</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-4.790330517340109</v>
+        <v>-4.774823829729982</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-7.264742769626849</v>
+        <v>-7.240251205870521</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-7.186333459543327</v>
+        <v>-7.162435440547135</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-5.43158773484754</v>
+        <v>-5.414552417424837</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>239</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>2.318277160961479</v>
+        <v>2.306495498997748</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>3.218303954037779</v>
+        <v>3.203481939109814</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>1.987101233857381</v>
+        <v>1.976530770755573</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>5.468458333091242</v>
+        <v>5.444842286130857</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>3.674462694249684</v>
+        <v>3.65786962833009</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>3.554544222948707</v>
+        <v>3.538540724869456</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>7.662798501865566</v>
+        <v>7.630205834944881</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>9.712631364794284</v>
+        <v>9.672519344771295</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>9.654548818406703</v>
+        <v>9.614710123720521</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>9.224680073751969</v>
+        <v>9.186600880595577</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>8.182586764674866</v>
+        <v>8.148991362234682</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>10.31837518879412</v>
+        <v>10.27677793672173</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>11.57988881401747</v>
+        <v>11.53295259174657</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>10.99494917006591</v>
+        <v>10.94946431897708</v>
       </c>
     </row>
     <row r="10">
@@ -780,49 +780,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-2.076771653543311</v>
+        <v>-2.08245869301107</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-3.689286739933131</v>
+        <v>-3.703021175788493</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-4.085306941248099</v>
+        <v>-4.100573297121407</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-1.453451837240131</v>
+        <v>-1.455839429247924</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.7412559837593804</v>
+        <v>-0.7407961924543542</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.4433612320805622</v>
+        <v>-0.4416722477086807</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>1.560078303330094</v>
+        <v>1.57325343735301</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.6750924546752302</v>
+        <v>0.6840184163137621</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>2.285544422783673</v>
+        <v>2.302080569591013</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>2.269696353974439</v>
+        <v>2.285924943002968</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>2.295019319391272</v>
+        <v>2.310523127592354</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>4.00254021347974</v>
+        <v>4.026386525735965</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>2.747713314014618</v>
+        <v>2.766477844481216</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>1.554663198140602</v>
+        <v>1.56864085988633</v>
       </c>
     </row>
     <row r="11">
@@ -832,49 +832,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>294</v>
+        <v>283</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-2.153302265788206</v>
+        <v>-2.206220219457038</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.1586575280636495</v>
+        <v>0.1876092115633199</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>1.648852592880438</v>
+        <v>1.737666827375207</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>2.638423010783725</v>
+        <v>2.776503449006647</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.9295418841249727</v>
+        <v>0.9985224192044484</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>3.78710825036336</v>
+        <v>3.966376027116929</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.5467958380249058</v>
+        <v>-0.512985175371405</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.1395767092340421</v>
+        <v>-0.09285499447339163</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-1.039225395483413</v>
+        <v>-1.023237205970773</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>1.382441439438111</v>
+        <v>1.490473069127674</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.8496080810064583</v>
+        <v>0.9295796034905095</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>2.424648590975551</v>
+        <v>2.572734107696071</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>2.202721324190655</v>
+        <v>2.346326957012892</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>4.479742903330973</v>
+        <v>4.716189632045364</v>
       </c>
     </row>
     <row r="12">
@@ -2213,10 +2213,8 @@
           <t>X &gt; 18.12</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>4064~4077</t>
-        </is>
+      <c r="B6" t="n">
+        <v>4064</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>-0.1510296864106095</v>
@@ -2267,10 +2265,8 @@
           <t>X &gt; 21.43</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>3927~3940</t>
-        </is>
+      <c r="B7" t="n">
+        <v>3927</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>-0.2853164927988061</v>
@@ -2321,10 +2317,8 @@
           <t>X &gt; 24.74</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>3722~3735</t>
-        </is>
+      <c r="B8" t="n">
+        <v>3722</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>-0.4720193108391584</v>
@@ -2375,10 +2369,8 @@
           <t>X &gt; 28.04</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>3522~3535</t>
-        </is>
+      <c r="B9" t="n">
+        <v>3522</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>-0.6688272876781554</v>
@@ -2429,10 +2421,8 @@
           <t>X &gt; 31.35</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>3283~3296</t>
-        </is>
+      <c r="B10" t="n">
+        <v>3283</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>-0.8854286114721077</v>
@@ -2483,10 +2473,8 @@
           <t>X &gt; 34.66</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>3045~3056</t>
-        </is>
+      <c r="B11" t="n">
+        <v>3045</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>-0.791867639581703</v>
@@ -2537,10 +2525,8 @@
           <t>X &gt; 37.97</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2762~2762</t>
-        </is>
+      <c r="B12" t="n">
+        <v>2762</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>-0.6469502680738444</v>
@@ -2591,10 +2577,8 @@
           <t>X &gt; 41.28</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2419~2419</t>
-        </is>
+      <c r="B13" t="n">
+        <v>2419</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>0.007595164701143631</v>
@@ -2645,10 +2629,8 @@
           <t>X &gt; 44.59</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2143~2143</t>
-        </is>
+      <c r="B14" t="n">
+        <v>2143</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>0.04972546887075424</v>
@@ -2699,10 +2681,8 @@
           <t>X &gt; 47.9</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>1878~1878</t>
-        </is>
+      <c r="B15" t="n">
+        <v>1878</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>0.009224086605783555</v>
@@ -2753,10 +2733,8 @@
           <t>X &gt; 51.2</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>1665~1665</t>
-        </is>
+      <c r="B16" t="n">
+        <v>1665</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>0.2392944125227601</v>
@@ -2807,10 +2785,8 @@
           <t>X &gt; 54.51</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1446~1446</t>
-        </is>
+      <c r="B17" t="n">
+        <v>1446</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>0.4111259951427257</v>
@@ -2861,10 +2837,8 @@
           <t>X &gt; 57.82</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>1204~1204</t>
-        </is>
+      <c r="B18" t="n">
+        <v>1204</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>0.2474254671654421</v>
@@ -2915,10 +2889,8 @@
           <t>X &gt; 61.13</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>1029~1029</t>
-        </is>
+      <c r="B19" t="n">
+        <v>1029</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>0.4706044397511491</v>
@@ -2969,10 +2941,8 @@
           <t>X &gt; 64.44</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>939~939</t>
-        </is>
+      <c r="B20" t="n">
+        <v>939</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>0.009224086605783555</v>
@@ -3023,10 +2993,8 @@
           <t>X &gt; 67.75</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>824~824</t>
-        </is>
+      <c r="B21" t="n">
+        <v>824</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>-0.1876130774915268</v>
@@ -3077,10 +3045,8 @@
           <t>X &gt; 71.05</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>655~655</t>
-        </is>
+      <c r="B22" t="n">
+        <v>655</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>0.3309891607060536</v>
@@ -3131,10 +3097,8 @@
           <t>X &gt; 74.36</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>534~534</t>
-        </is>
+      <c r="B23" t="n">
+        <v>534</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>0.8773481966439576</v>
@@ -3185,10 +3149,8 @@
           <t>X &gt; 77.67</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>469~469</t>
-        </is>
+      <c r="B24" t="n">
+        <v>469</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>1.237904963372117</v>
@@ -3239,10 +3201,8 @@
           <t>X &gt; 80.98</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>373~373</t>
-        </is>
+      <c r="B25" t="n">
+        <v>373</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>2.198250687832925</v>
@@ -3293,10 +3253,8 @@
           <t>X &gt; 84.29</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>306~306</t>
-        </is>
+      <c r="B26" t="n">
+        <v>306</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>0.1209407647573499</v>
@@ -3347,10 +3305,8 @@
           <t>X &gt; 87.6</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>268~268</t>
-        </is>
+      <c r="B27" t="n">
+        <v>268</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>-1.000901006777134</v>
@@ -3401,10 +3357,8 @@
           <t>X &gt; 90.9</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>239~239</t>
-        </is>
+      <c r="B28" t="n">
+        <v>239</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>-0.1921830900844554</v>
@@ -3455,10 +3409,8 @@
           <t>X &gt; 94.21</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>217~217</t>
-        </is>
+      <c r="B29" t="n">
+        <v>217</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>0.04112389177158349</v>
@@ -3509,10 +3461,8 @@
           <t>X &gt; 97.52</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>190~190</t>
-        </is>
+      <c r="B30" t="n">
+        <v>190</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>0.1381406271584424</v>
@@ -3563,10 +3513,8 @@
           <t>X &gt; 100.8</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>165~165</t>
-        </is>
+      <c r="B31" t="n">
+        <v>165</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>-0.3722261989978506</v>
@@ -3617,10 +3565,8 @@
           <t>X &gt; 104.1</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>144~144</t>
-        </is>
+      <c r="B32" t="n">
+        <v>144</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>0.2843394575678033</v>
@@ -3671,10 +3617,8 @@
           <t>X &gt; 107.4</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>119~119</t>
-        </is>
+      <c r="B33" t="n">
+        <v>119</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>0.4477381503782638</v>
@@ -3725,10 +3669,8 @@
           <t>X &gt; 110.8</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>102~102</t>
-        </is>
+      <c r="B34" t="n">
+        <v>102</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>0.4477381503782638</v>
@@ -3779,10 +3721,8 @@
           <t>X &gt; 114.1</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>84~84</t>
-        </is>
+      <c r="B35" t="n">
+        <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>2.268466441694791</v>
@@ -3967,10 +3907,8 @@
           <t>X &lt; 18.12</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>84~84</t>
-        </is>
+      <c r="B6" t="n">
+        <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>9.41132358455193</v>
@@ -4021,10 +3959,8 @@
           <t>X &lt; 21.43</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>221~221</t>
-        </is>
+      <c r="B7" t="n">
+        <v>221</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>5.877602403771931</v>
@@ -4075,10 +4011,8 @@
           <t>X &lt; 24.74</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>426~426</t>
-        </is>
+      <c r="B8" t="n">
+        <v>426</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>4.548815200916785</v>
@@ -4129,10 +4063,8 @@
           <t>X &lt; 28.04</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>626~626</t>
-        </is>
+      <c r="B9" t="n">
+        <v>626</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>4.056082446563188</v>
@@ -4183,10 +4115,8 @@
           <t>X &lt; 31.35</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>865~865</t>
-        </is>
+      <c r="B10" t="n">
+        <v>865</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>3.575925841639737</v>
@@ -4237,10 +4167,8 @@
           <t>X &lt; 34.66</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>1103~1105</t>
-        </is>
+      <c r="B11" t="n">
+        <v>1103</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>2.348190639066047</v>
@@ -4291,10 +4219,8 @@
           <t>X &lt; 37.97</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>1386~1399</t>
-        </is>
+      <c r="B12" t="n">
+        <v>1386</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>1.402201422463364</v>
@@ -4345,10 +4271,8 @@
           <t>X &lt; 41.28</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>1729~1742</t>
-        </is>
+      <c r="B13" t="n">
+        <v>1729</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>0.08979933765454717</v>
@@ -4399,10 +4323,8 @@
           <t>X &lt; 44.59</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2005~2018</t>
-        </is>
+      <c r="B14" t="n">
+        <v>2005</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>0.03381638742134641</v>
@@ -4453,10 +4375,8 @@
           <t>X &lt; 47.9</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2270~2283</t>
-        </is>
+      <c r="B15" t="n">
+        <v>2270</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>0.06897955101210584</v>
@@ -4507,10 +4427,8 @@
           <t>X &lt; 51.2</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2483~2496</t>
-        </is>
+      <c r="B16" t="n">
+        <v>2483</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>-0.08959216636382195</v>
@@ -4561,10 +4479,8 @@
           <t>X &lt; 54.51</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2702~2715</t>
-        </is>
+      <c r="B17" t="n">
+        <v>2702</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>-0.1545801249981835</v>
@@ -4615,10 +4531,8 @@
           <t>X &lt; 57.82</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2944~2957</t>
-        </is>
+      <c r="B18" t="n">
+        <v>2944</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>-0.04162905406185757</v>
@@ -4669,10 +4583,8 @@
           <t>X &lt; 61.13</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>3119~3132</t>
-        </is>
+      <c r="B19" t="n">
+        <v>3119</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>-0.09880230488430897</v>
@@ -4723,10 +4635,8 @@
           <t>X &lt; 64.44</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>3209~3222</t>
-        </is>
+      <c r="B20" t="n">
+        <v>3209</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>0.05156478345234916</v>
@@ -4777,10 +4687,8 @@
           <t>X &lt; 67.75</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>3324~3337</t>
-        </is>
+      <c r="B21" t="n">
+        <v>3324</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>0.09871031628987481</v>
@@ -4831,10 +4739,8 @@
           <t>X &lt; 71.05</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>3493~3506</t>
-        </is>
+      <c r="B22" t="n">
+        <v>3493</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>-0.01197796653056571</v>
@@ -4885,10 +4791,8 @@
           <t>X &lt; 74.36</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>3614~3627</t>
-        </is>
+      <c r="B23" t="n">
+        <v>3614</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>-0.08097623032853818</v>
@@ -4939,10 +4843,8 @@
           <t>X &lt; 77.67</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>3679~3692</t>
-        </is>
+      <c r="B24" t="n">
+        <v>3679</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>-0.1099063592132197</v>
@@ -4993,10 +4895,8 @@
           <t>X &lt; 80.98</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>3775~3788</t>
-        </is>
+      <c r="B25" t="n">
+        <v>3775</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>-0.1703126602310974</v>
@@ -5047,10 +4947,8 @@
           <t>X &lt; 84.29</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>3842~3855</t>
-        </is>
+      <c r="B26" t="n">
+        <v>3842</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>0.03574455916746189</v>
@@ -5101,10 +4999,8 @@
           <t>X &lt; 87.6</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>3880~3893</t>
-        </is>
+      <c r="B27" t="n">
+        <v>3880</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>0.1138054506608199</v>
@@ -5155,10 +5051,8 @@
           <t>X &lt; 90.9</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>3909~3922</t>
-        </is>
+      <c r="B28" t="n">
+        <v>3909</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>0.05628121064162883</v>
@@ -5209,10 +5103,8 @@
           <t>X &lt; 94.21</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>3931~3944</t>
-        </is>
+      <c r="B29" t="n">
+        <v>3931</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>0.04205863719367642</v>
@@ -5263,10 +5155,8 @@
           <t>X &lt; 97.52</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>3958~3971</t>
-        </is>
+      <c r="B30" t="n">
+        <v>3958</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>0.0374103325223345</v>
@@ -5317,10 +5207,8 @@
           <t>X &lt; 100.8</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>3983~3996</t>
-        </is>
+      <c r="B31" t="n">
+        <v>3983</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>0.05911423234257995</v>
@@ -5371,10 +5259,8 @@
           <t>X &lt; 104.1</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>4004~4017</t>
-        </is>
+      <c r="B32" t="n">
+        <v>4004</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>0.03332294441536732</v>
@@ -5425,10 +5311,8 @@
           <t>X &lt; 107.4</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>4029~4042</t>
-        </is>
+      <c r="B33" t="n">
+        <v>4029</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>0.03006489601961704</v>
@@ -5479,10 +5363,8 @@
           <t>X &lt; 110.8</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>4046~4059</t>
-        </is>
+      <c r="B34" t="n">
+        <v>4046</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>0.03181420504255783</v>
@@ -5533,10 +5415,8 @@
           <t>X &lt; 114.1</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>4064~4077</t>
-        </is>
+      <c r="B35" t="n">
+        <v>4064</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>-0.003862651826359809</v>

--- a/workspaces/btc_daily_14days/volatility/realized_vol_30.xlsx
+++ b/workspaces/btc_daily_14days/volatility/realized_vol_30.xlsx
@@ -479,7 +479,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that Realized VOL-30 is approximately at value x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that Realized VOL-30 is approximately at value x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -575,46 +575,46 @@
         <v>137</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>3.69819869816228</v>
+        <v>3.710681881891574</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>8.641904181726154</v>
+        <v>8.654780473844326</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>14.07309042107627</v>
+        <v>14.08607059320645</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>10.56634301493975</v>
+        <v>10.57929542148309</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>11.48845021751178</v>
+        <v>11.50153716355566</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>8.146033441547473</v>
+        <v>8.159053545350616</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>13.89269916891332</v>
+        <v>13.90574798929573</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>14.15849201283572</v>
+        <v>14.17165806320124</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>14.10136707864242</v>
+        <v>14.11455324332009</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>12.52645307014659</v>
+        <v>12.53984756237682</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>10.86637742706458</v>
+        <v>10.87982637641217</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>8.714897232551863</v>
+        <v>8.7283436872412</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>8.297033122871433</v>
+        <v>8.310586201990603</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>8.548951232210428</v>
+        <v>8.538521596512275</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>205</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>3.104478086450818</v>
+        <v>3.116957448691025</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.03979370475792621</v>
+        <v>0.05266016189390399</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-1.327492515702311</v>
+        <v>-1.31452601366292</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-1.197352992274759</v>
+        <v>-1.18441082403735</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.7614130854154055</v>
+        <v>-0.748335601441859</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.02234842308095608</v>
+        <v>0.03536217837093147</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.06235402768893294</v>
+        <v>-0.04931322380809888</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-2.476856130184366</v>
+        <v>-2.463698099844422</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-2.050938498899882</v>
+        <v>-2.037758860191097</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-1.438728904939381</v>
+        <v>-1.425339094137392</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-2.130871247554325</v>
+        <v>-2.117425665975929</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.6342481052585072</v>
+        <v>-0.6208034216982696</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.4086177540060874</v>
+        <v>0.4221700457084694</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>1.634228070380495</v>
+        <v>1.623798434682122</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>200</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>2.993769161295631</v>
+        <v>3.006243876254622</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.8903775634259432</v>
+        <v>0.9032399235154003</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-1.497502768854474</v>
+        <v>-1.484541127129852</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-1.866008778261218</v>
+        <v>-1.853071436079752</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-2.403524525210685</v>
+        <v>-2.390452059580014</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-1.608231130417693</v>
+        <v>-1.595221727688511</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-2.691408479634362</v>
+        <v>-2.678372038163545</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-4.65575585000586</v>
+        <v>-4.642601597955952</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-3.219797691713801</v>
+        <v>-3.206620776393294</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-5.068663691058042</v>
+        <v>-5.055276833156967</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-4.774823829729982</v>
+        <v>-4.761380270922949</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-7.240251205870521</v>
+        <v>-7.226808460774244</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-7.162435440547135</v>
+        <v>-7.148884181243361</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-5.414552417424837</v>
+        <v>-5.424982053122754</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>239</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>2.306495498997748</v>
+        <v>2.318963572720875</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>3.203481939109814</v>
+        <v>3.216340731550765</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>1.976530770755573</v>
+        <v>1.989489787937956</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>5.444842286130857</v>
+        <v>5.457780671002375</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>3.65786962833009</v>
+        <v>3.670941845249956</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>3.538540724869456</v>
+        <v>3.551549374343374</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>7.630205834944881</v>
+        <v>7.64324482703465</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>9.672519344771295</v>
+        <v>9.685677710760523</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>9.614710123720521</v>
+        <v>9.627889917756036</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>9.186600880595577</v>
+        <v>9.199990378866232</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>8.148991362234682</v>
+        <v>8.162436533949403</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>10.27677793672173</v>
+        <v>10.29022250100848</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>11.53295259174657</v>
+        <v>11.54650487000748</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>10.94946431897708</v>
+        <v>10.93903468327883</v>
       </c>
     </row>
     <row r="10">
@@ -780,49 +780,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-2.08245869301107</v>
+        <v>-2.064534185360678</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-3.703021175788493</v>
+        <v>-3.677064426710096</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-4.100573297121407</v>
+        <v>-4.073059285928387</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-1.455839429247924</v>
+        <v>-1.440573840868552</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.7407961924543542</v>
+        <v>-0.7280963904833442</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.4416722477086807</v>
+        <v>-0.4302020636559263</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>1.57325343735301</v>
+        <v>1.573847323054771</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.6840184163137621</v>
+        <v>0.6887666767368614</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>2.302080569591013</v>
+        <v>2.299626491476722</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>2.285924943002968</v>
+        <v>2.283975188319573</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>2.310523127592354</v>
+        <v>2.079049749827441</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>4.026386525735965</v>
+        <v>4.017186284635336</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>2.766477844481216</v>
+        <v>2.762211457184613</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>1.56864085988633</v>
+        <v>1.734013762776918</v>
       </c>
     </row>
     <row r="11">
@@ -835,46 +835,46 @@
         <v>283</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-2.206220219457038</v>
+        <v>-2.375671853640959</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.1876092115633199</v>
+        <v>0.01208728309524787</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>1.737666827375207</v>
+        <v>1.560965578355173</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>2.776503449006647</v>
+        <v>2.601150131559258</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.9985224192044484</v>
+        <v>0.8210987905153075</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>3.966376027116929</v>
+        <v>3.78979955068268</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.512985175371405</v>
+        <v>-0.6878126042604578</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.09285499447339163</v>
+        <v>-0.2695421613935665</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-1.023237205970773</v>
+        <v>-1.199799671352643</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>1.490473069127674</v>
+        <v>1.310864360982919</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.9295796034905095</v>
+        <v>0.9430368972007273</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>2.572734107696071</v>
+        <v>2.392466174395338</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>2.346326957012892</v>
+        <v>2.164991481377719</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>4.716189632045364</v>
+        <v>4.705759996347211</v>
       </c>
     </row>
     <row r="12">
@@ -887,46 +887,46 @@
         <v>343</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-5.263117620501518</v>
+        <v>-5.250595330825895</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-4.833874906935165</v>
+        <v>-4.820965097359114</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-6.68646956105362</v>
+        <v>-6.673462429636018</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-9.180123133985482</v>
+        <v>-9.167143991587018</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-7.386182833022666</v>
+        <v>-7.373072028647726</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-7.963376463820126</v>
+        <v>-7.95033356752576</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-8.048110181092405</v>
+        <v>-8.035043926791928</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-8.806838769378274</v>
+        <v>-8.793657760083036</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-9.742474224073696</v>
+        <v>-9.729275485118933</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-12.05032535662356</v>
+        <v>-12.03692022897073</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-12.25507868094107</v>
+        <v>-12.24162138723085</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-11.05451476557821</v>
+        <v>-11.0410624768581</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-10.8916789975143</v>
+        <v>-10.87812295116269</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-9.475776907220521</v>
+        <v>-9.486206542918673</v>
       </c>
     </row>
     <row r="13">
@@ -939,46 +939,46 @@
         <v>276</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.3195252767317172</v>
+        <v>-0.3070029870560944</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.6051329943620019</v>
+        <v>0.618042803938053</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.152054552814306</v>
+        <v>-0.1390474213967039</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-2.195714463685064</v>
+        <v>-2.1827353212866</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-2.371816838177523</v>
+        <v>-2.358706033802584</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-2.436693741041573</v>
+        <v>-2.423650844747208</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.01480442574412422</v>
+        <v>0.02787068004460025</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.4523789730372911</v>
+        <v>-0.4391979637420533</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-1.238016540379107</v>
+        <v>-1.224817801424344</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-1.001185203667895</v>
+        <v>-0.9877800760150635</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-1.568257368565099</v>
+        <v>-1.554800074854882</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.8092365300602538</v>
+        <v>-0.7957842413401437</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.5821030618933136</v>
+        <v>0.5956591082449165</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.2551321275695244</v>
+        <v>-0.2655617632676766</v>
       </c>
     </row>
     <row r="14">
@@ -991,46 +991,46 @@
         <v>265</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.3367503590353067</v>
+        <v>0.3492726487109294</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.8974647633629118</v>
+        <v>-0.8845549537868607</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.9718174734367651</v>
+        <v>0.9848246048543672</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>2.611504568308419</v>
+        <v>2.624483710706883</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>3.959875806066393</v>
+        <v>3.972986610441332</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>3.125242272083938</v>
+        <v>3.138285168378303</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>1.531074592547512</v>
+        <v>1.544140846847988</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>3.32804213716215</v>
+        <v>3.341223146457388</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>2.889683760413895</v>
+        <v>2.902882499368658</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>3.54899253765003</v>
+        <v>3.562397665302861</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>2.58952223220038</v>
+        <v>2.602979525910598</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.3597544461495801</v>
+        <v>0.3732067348696901</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-1.569934127059383</v>
+        <v>-1.55637808070778</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.1881373230849803</v>
+        <v>-0.1985669587831325</v>
       </c>
     </row>
     <row r="15">
@@ -1043,46 +1043,46 @@
         <v>213</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-1.789212968097303</v>
+        <v>-1.77669067842168</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.3550819635393836</v>
+        <v>0.3679917731154347</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-3.32617171958308</v>
+        <v>-3.313164588165478</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-6.012819995426284</v>
+        <v>-5.99984085302782</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-7.020724778573523</v>
+        <v>-7.007613974198584</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-9.070700681233447</v>
+        <v>-9.057657784939082</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-9.155434398505676</v>
+        <v>-9.1423681442052</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-8.683650661136937</v>
+        <v>-8.670469651841699</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-9.683617683469528</v>
+        <v>-9.670418944514765</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-11.00322643657247</v>
+        <v>-10.98982130891964</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-8.860561920514563</v>
+        <v>-8.847104626804345</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-13.99049801199543</v>
+        <v>-13.97704572327532</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-16.28868689524074</v>
+        <v>-16.27513084888913</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-17.44741626718981</v>
+        <v>-17.45784590288796</v>
       </c>
     </row>
     <row r="16">
@@ -1095,46 +1095,46 @@
         <v>219</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.8952648042282405</v>
+        <v>-0.8827425145526178</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>3.885855646734448</v>
+        <v>3.8987654563105</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>3.490986940137859</v>
+        <v>3.503994071555461</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>4.534482081877776</v>
+        <v>4.54746122427624</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>2.626197853106973</v>
+        <v>2.639308657481912</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>2.010397781690209</v>
+        <v>2.023440677984574</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.3574409584131644</v>
+        <v>-0.3443747041126883</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>2.371722674768804</v>
+        <v>2.384903684064042</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>3.22396479771897</v>
+        <v>3.237163536673734</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>5.113565640088304</v>
+        <v>5.126970767741135</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>4.452191311204523</v>
+        <v>4.46564860491474</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>7.682921500513416</v>
+        <v>7.696373789233526</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>7.719287894134673</v>
+        <v>7.732843940486276</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>3.402799180748858</v>
+        <v>3.392369545050705</v>
       </c>
     </row>
     <row r="17">
@@ -1147,46 +1147,46 @@
         <v>242</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>1.225569944252832</v>
+        <v>1.238092233928455</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.4404426122802647</v>
+        <v>0.4533524218563159</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1.698466467667195</v>
+        <v>1.711473599084798</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-3.956404366667456</v>
+        <v>-3.943425224268992</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-2.841933019756148</v>
+        <v>-2.828822215381209</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-2.957714222536367</v>
+        <v>-2.944671326242002</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-2.629224799312766</v>
+        <v>-2.61615854501229</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-1.856738776606669</v>
+        <v>-1.843557767311431</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-1.91773866278897</v>
+        <v>-1.904539923834207</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-1.941417566825166</v>
+        <v>-1.928012439172335</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-3.385840312630343</v>
+        <v>-3.372383018920125</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-2.111787733797314</v>
+        <v>-2.098335445077204</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-2.945265485238082</v>
+        <v>-2.931709438886479</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-3.10876729345766</v>
+        <v>-3.119196929155812</v>
       </c>
     </row>
     <row r="18">
@@ -1199,46 +1199,46 @@
         <v>175</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-1.064866891638552</v>
+        <v>-1.052344601962929</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-8.390726218888517</v>
+        <v>-8.377816409312466</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-11.07130921119939</v>
+        <v>-11.05830207978179</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-12.08391322144897</v>
+        <v>-12.07093407905051</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-12.62233443652121</v>
+        <v>-12.60922363214627</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-14.0391782130912</v>
+        <v>-14.02613531679683</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-16.98105478750633</v>
+        <v>-16.96798853320585</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-15.73395247200218</v>
+        <v>-15.72077146270694</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-18.08066664389877</v>
+        <v>-18.067467904944</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-14.9307918289267</v>
+        <v>-14.91738670127387</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-13.9926880103872</v>
+        <v>-13.97923071667698</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-13.3868762816132</v>
+        <v>-13.37342399289309</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-9.235702321129459</v>
+        <v>-9.222146274777856</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-9.557409560281741</v>
+        <v>-9.567839195979893</v>
       </c>
     </row>
     <row r="19">
@@ -1251,46 +1251,46 @@
         <v>90</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>5.284339457567796</v>
+        <v>5.296861747243419</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>8.11721028904811</v>
+        <v>8.130120098624161</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>4.389008249118071</v>
+        <v>4.402015380535673</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>7.852594715058899</v>
+        <v>7.865573857457363</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>7.314173499986609</v>
+        <v>7.327284304361548</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>7.61161543770227</v>
+        <v>7.624658333996635</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>7.526881720430111</v>
+        <v>7.539947974730588</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>11.50414276609305</v>
+        <v>11.51732377538828</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>12.55425399102199</v>
+        <v>12.56745272997675</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>9.48190658377159</v>
+        <v>9.495311711424421</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>8.166042148343152</v>
+        <v>8.17949944205337</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>9.311536416799569</v>
+        <v>9.324988705519679</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>5.557948472521453</v>
+        <v>5.571504518873056</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>2.474336471464291</v>
+        <v>2.463906835766139</v>
       </c>
     </row>
     <row r="20">
@@ -1303,46 +1303,46 @@
         <v>115</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1.419605158050892</v>
+        <v>1.432127447726515</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-2.800664107087329</v>
+        <v>-2.787754297511277</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.5868371615099548</v>
+        <v>-0.5738300300923527</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-2.195714463685164</v>
+        <v>-2.1827353212867</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.7441251908080844</v>
+        <v>0.7572359951830236</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-2.436693741041516</v>
+        <v>-2.423650844747151</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.9568334112512673</v>
+        <v>0.9698996655517433</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1.359215229861171</v>
+        <v>1.372396239156409</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-3.049610743277753</v>
+        <v>-3.03641200432299</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-4.769301145696737</v>
+        <v>-4.755896018043906</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-10.19144577436224</v>
+        <v>-10.17798848065202</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-10.15706261701676</v>
+        <v>-10.14361032829665</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-8.838186793179247</v>
+        <v>-8.824630746827644</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-10.32759589568547</v>
+        <v>-10.33802553138362</v>
       </c>
     </row>
     <row r="21">
@@ -1355,46 +1355,46 @@
         <v>169</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-2.197580332044296</v>
+        <v>-2.185058042368674</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-2.034006016014466</v>
+        <v>-2.021096206438415</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>3.48828504070255</v>
+        <v>3.501292172120152</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>7.168834031298218</v>
+        <v>7.181813173696682</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>4.263548910900603</v>
+        <v>4.276659715275542</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>6.336138777610316</v>
+        <v>6.349181673904681</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>4.476257131343985</v>
+        <v>4.489323385644461</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>4.009073732562456</v>
+        <v>4.022254741857694</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.3977779883920434</v>
+        <v>0.4109767273468066</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-2.819211101961393</v>
+        <v>-2.805805974308562</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>2.301479360703283</v>
+        <v>2.314936654413501</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>2.927578494380107</v>
+        <v>2.941030783100217</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>6.649335717754731</v>
+        <v>6.662891764106334</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>5.715625097368296</v>
+        <v>5.705195461670144</v>
       </c>
     </row>
     <row r="22">
@@ -1407,46 +1407,46 @@
         <v>121</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-2.080215179714109</v>
+        <v>-2.067692890038487</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-6.171127635653527</v>
+        <v>-6.158217826077475</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-7.392442623241941</v>
+        <v>-7.379435491824339</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-4.782850647659188</v>
+        <v>-4.769871505260724</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-3.668379300747894</v>
+        <v>-3.655268496372955</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-3.370937363032233</v>
+        <v>-3.357894466737868</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-2.629224799312823</v>
+        <v>-2.616158545012347</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-3.922854479085956</v>
+        <v>-3.909673469790718</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>2.627715882665527</v>
+        <v>2.64091462162029</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.95114441664591</v>
+        <v>0.9645495442987411</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.7463910923283308</v>
+        <v>0.7598483860385485</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.872118312309702</v>
+        <v>-0.858666023589592</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>1.186965919720549</v>
+        <v>1.200521966072152</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>3.916026094972047</v>
+        <v>3.905596459273895</v>
       </c>
     </row>
     <row r="23">
@@ -1459,46 +1459,46 @@
         <v>65</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-1.724207550979209</v>
+        <v>-1.711685261303586</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-4.874242702405091</v>
+        <v>-4.86133289282904</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-6.807572947463044</v>
+        <v>-6.794565816045441</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-6.677319814855629</v>
+        <v>-6.664340672457165</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-8.754202568389339</v>
+        <v>-8.741091764014399</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-8.456760630673678</v>
+        <v>-8.443717734379312</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-5.464571271022791</v>
+        <v>-5.451505016722315</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-1.316370054419764</v>
+        <v>-1.303189045124526</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.1610915978594747</v>
+        <v>0.1742903368142379</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>2.387889489754627</v>
+        <v>2.401294617407459</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>2.183136165436956</v>
+        <v>2.196593459147174</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-3.936326831063589</v>
+        <v>-3.922874542343479</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-4.356581442008491</v>
+        <v>-4.343025395656888</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-1.029937032809123</v>
+        <v>-1.040366668507275</v>
       </c>
     </row>
     <row r="24">
@@ -1511,46 +1511,46 @@
         <v>96</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-2.493438320209975</v>
+        <v>-2.480916030534353</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>2.144988066825803</v>
+        <v>2.157897876401854</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>2.791786026895842</v>
+        <v>2.804793158313444</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>5.005372492836713</v>
+        <v>5.018351635235177</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>7.591951277764508</v>
+        <v>7.605062082139447</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>6.847726548813526</v>
+        <v>6.860769445107891</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>2.596326164874554</v>
+        <v>2.60939241917503</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-2.037523900573611</v>
+        <v>-2.024342891278373</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>5.193142879910788</v>
+        <v>5.206341618865551</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>5.384684361549517</v>
+        <v>5.398089489202349</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>8.304931037231981</v>
+        <v>8.318388330942199</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>4.17264752791062</v>
+        <v>4.18609981663073</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>7.919059583632468</v>
+        <v>7.93261562998407</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>5.043780915908755</v>
+        <v>5.033351280210603</v>
       </c>
     </row>
     <row r="25">
@@ -1563,46 +1563,46 @@
         <v>67</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>11.68566615740191</v>
+        <v>11.69818844707753</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>8.58155523100492</v>
+        <v>8.594465040580971</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>11.17176115127396</v>
+        <v>11.18476828269156</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>14.28708891074708</v>
+        <v>14.30006805314554</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>15.24120500910774</v>
+        <v>15.25431581348268</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>17.03118426025625</v>
+        <v>17.04422715655062</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>15.45391322955118</v>
+        <v>15.46697948385166</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>12.00165520390396</v>
+        <v>12.0148362131992</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>10.44811800428882</v>
+        <v>10.46131674324359</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>15.56814207299225</v>
+        <v>15.58154720064508</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>15.36338874867469</v>
+        <v>15.37684604238491</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>16.89030921945297</v>
+        <v>16.90376150817308</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>10.49990535477668</v>
+        <v>10.51346140112828</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>16.71977594078426</v>
+        <v>16.70934630508611</v>
       </c>
     </row>
     <row r="26">
@@ -1615,46 +1615,46 @@
         <v>38</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>8.03287746926371</v>
+        <v>8.045399758939332</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>11.6844617510363</v>
+        <v>11.69737156061235</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>8.65801409707128</v>
+        <v>8.671021228488883</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>11.41984617704727</v>
+        <v>11.43282531944573</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>16.14458285671203</v>
+        <v>16.15769366108697</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>19.07360374179595</v>
+        <v>19.08664663809031</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>16.35729107715526</v>
+        <v>16.37035733145574</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>18.52168662574233</v>
+        <v>18.53486763503756</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>23.72384463429672</v>
+        <v>23.73704337325148</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>25.50529839663729</v>
+        <v>25.51870352429012</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>20.0373871775828</v>
+        <v>20.05084447129302</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>14.8086124401913</v>
+        <v>14.82206472891141</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>17.01993677661498</v>
+        <v>17.03349282296658</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>9.374921266785989</v>
+        <v>9.364491631087837</v>
       </c>
     </row>
     <row r="27">
@@ -1667,46 +1667,46 @@
         <v>29</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-7.665852113313321</v>
+        <v>-7.653329823637698</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-5.829149864208716</v>
+        <v>-5.816240054632665</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-6.224018570805306</v>
+        <v>-6.211011439387704</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-6.093765438197806</v>
+        <v>-6.080786295799342</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>7.160916795005789</v>
+        <v>7.174027599380729</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>4.010082870652681</v>
+        <v>4.023125766947047</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>7.373625015449171</v>
+        <v>7.386691269749647</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>0.009889892529734823</v>
+        <v>0.02307090182497262</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-6.947661717790496</v>
+        <v>-6.934462978835732</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-7.797786902818423</v>
+        <v>-7.784381775165592</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-1.105988502997974</v>
+        <v>-1.092531209287756</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-11.41643293185933</v>
+        <v>-11.40298064313922</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-15.2849634048733</v>
+        <v>-15.2714073585217</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-15.03524207259701</v>
+        <v>-15.04567170829517</v>
       </c>
     </row>
     <row r="28">
@@ -1719,46 +1719,46 @@
         <v>22</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-2.493438320209911</v>
+        <v>-2.480916030534289</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.4404426122802505</v>
+        <v>0.4533524218563016</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>13.68193754204735</v>
+        <v>13.69494467346495</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>18.35764522010927</v>
+        <v>18.37062436250773</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>22.36467855049177</v>
+        <v>22.37778935486671</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.06515223906541223</v>
+        <v>-0.05210934277104684</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>8.941023134571658</v>
+        <v>8.954089388872134</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>3.928385190335419</v>
+        <v>3.941566199630657</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>3.867385304153245</v>
+        <v>3.880584043108009</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>12.10816921003428</v>
+        <v>12.12157433768711</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>16.44887043117131</v>
+        <v>16.46232772488153</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>11.93779904306233</v>
+        <v>11.95125133178244</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-2.118819204246471</v>
+        <v>-2.105263157894868</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-15.50546150833382</v>
+        <v>-15.51589114403198</v>
       </c>
     </row>
     <row r="29">
@@ -1771,46 +1771,46 @@
         <v>27</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.6415864683581702</v>
+        <v>-0.6290641786825475</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-2.253160081322271</v>
+        <v>-2.24025027174622</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>1.055674915784678</v>
+        <v>1.06868204720228</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-6.22147935901512</v>
+        <v>-6.208500216616656</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-10.46360427779105</v>
+        <v>-10.45049347341611</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-6.462458636371686</v>
+        <v>-6.44941574007732</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0.8602150537634472</v>
+        <v>0.8732813080639232</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-7.014375752425359</v>
+        <v>-7.001194743130121</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0.332031768799645</v>
+        <v>0.3452305077544082</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-4.221797119931878</v>
+        <v>-4.208391992279047</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>10.38826437056524</v>
+        <v>10.40172166427546</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>14.12635123161428</v>
+        <v>14.13980352033439</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>17.40980032437313</v>
+        <v>17.42335637072473</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>17.65952165664963</v>
+        <v>17.64909202095148</v>
       </c>
     </row>
     <row r="30">
@@ -1823,46 +1823,46 @@
         <v>25</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>3.506561679790032</v>
+        <v>3.519083969465655</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-2.105011933174289</v>
+        <v>-2.092102123598238</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-6.499880639770822</v>
+        <v>-6.48687350835322</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>1.630372492836564</v>
+        <v>1.643351635235028</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>13.09195127776451</v>
+        <v>13.10506208213945</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>17.38939321548011</v>
+        <v>17.40243611177448</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>17.30465949820783</v>
+        <v>17.31772575250831</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>16.83747609942633</v>
+        <v>16.85065710872157</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>16.77647621324414</v>
+        <v>16.78967495219891</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>15.9263510282161</v>
+        <v>15.93975615586893</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>7.721597703898581</v>
+        <v>7.735054997608799</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>11.75598086124401</v>
+        <v>11.76943314996412</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>11.33572625029917</v>
+        <v>11.34928229665077</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>11.58544758257534</v>
+        <v>11.57501794687719</v>
       </c>
     </row>
     <row r="31">
@@ -1875,46 +1875,46 @@
         <v>21</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-4.874390701162362</v>
+        <v>-4.861868411486739</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>12.56165473349242</v>
+        <v>12.57456454306848</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>12.16678602689591</v>
+        <v>12.17979315831351</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>12.29703915950341</v>
+        <v>12.31001830190187</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>16.52052270633594</v>
+        <v>16.53363351071088</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>16.81796464405167</v>
+        <v>16.83100754034604</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>11.97132616487462</v>
+        <v>11.98439241917509</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>1.980333242283528</v>
+        <v>1.993514251578766</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>11.44314287991075</v>
+        <v>11.45634161886551</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>10.59301769488282</v>
+        <v>10.60642282253565</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>10.38826437056524</v>
+        <v>10.40172166427546</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>5.660742766005917</v>
+        <v>5.674195054726027</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>5.240488155061016</v>
+        <v>5.254044201412619</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>5.490209487337303</v>
+        <v>5.479779851639151</v>
       </c>
     </row>
     <row r="32">
@@ -1927,46 +1927,46 @@
         <v>25</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.4934383202099752</v>
+        <v>-0.4809160305343525</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-14.10501193317429</v>
+        <v>-14.09210212359824</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-10.49988063977082</v>
+        <v>-10.48687350835322</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-6.369627507163322</v>
+        <v>-6.356648364764858</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-10.90804872223549</v>
+        <v>-10.89493791786055</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>1.389393215480176</v>
+        <v>1.402436111774541</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>5.30465949820789</v>
+        <v>5.317725752508366</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>4.837476099426368</v>
+        <v>4.850657108721606</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0.776476213244095</v>
+        <v>0.7896749521988582</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>3.92635102821616</v>
+        <v>3.939756155868992</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>3.721597703898524</v>
+        <v>3.735054997608742</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>3.755980861244012</v>
+        <v>3.769433149964122</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>3.335726250299111</v>
+        <v>3.349282296650713</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>3.585447582575398</v>
+        <v>3.575017946877246</v>
       </c>
     </row>
     <row r="33">
@@ -1979,46 +1979,46 @@
         <v>17</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.4477381503782638</v>
+        <v>0.4602604400538866</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-1.163835462585915</v>
+        <v>-1.150925653009864</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-13.32341005153553</v>
+        <v>-13.31040292011793</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-19.0755098601045</v>
+        <v>-19.06253071770603</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-25.49628401635314</v>
+        <v>-25.4831732119782</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-25.19884207863748</v>
+        <v>-25.18579918234311</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-19.40122285473328</v>
+        <v>-19.38815660043281</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-13.98605331233827</v>
+        <v>-13.97287230304303</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-14.04705319852062</v>
+        <v>-14.03385445956586</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-14.89717838354855</v>
+        <v>-14.88377325589572</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-9.219578766689573</v>
+        <v>-9.206121472979355</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-9.185195609344227</v>
+        <v>-9.171743320624117</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-9.605450220289129</v>
+        <v>-9.591894173937526</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-9.355728888012877</v>
+        <v>-9.366158523711029</v>
       </c>
     </row>
     <row r="34">
@@ -2031,46 +2031,46 @@
         <v>18</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-8.048993875765532</v>
+        <v>-8.03647158608991</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-15.21612304428534</v>
+        <v>-15.20321323470929</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-21.16654730643753</v>
+        <v>-21.15354017501993</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-21.03629417383003</v>
+        <v>-21.02331503143157</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-27.13027094445771</v>
+        <v>-27.11716014008277</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-21.2772734511865</v>
+        <v>-21.26423055489214</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-32.47311827956989</v>
+        <v>-32.46005202526941</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-27.38474612279583</v>
+        <v>-27.37156511350059</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-27.44574600897813</v>
+        <v>-27.43254727002337</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-28.29587119400606</v>
+        <v>-28.28246606635323</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-34.0561800738792</v>
+        <v>-34.04272278016898</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-45.13290802764487</v>
+        <v>-45.11945573892477</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-51.10871819414533</v>
+        <v>-51.09516214779373</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-50.85899686186901</v>
+        <v>-50.86942649756716</v>
       </c>
     </row>
   </sheetData>
@@ -2121,7 +2121,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that Realized VOL-30 is above threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that Realized VOL-30 is above threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -2214,49 +2214,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4064</v>
+        <v>4065</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.1510296864106095</v>
+        <v>-0.151342710279323</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.1305271441653986</v>
+        <v>-0.1308561093720328</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.266751805414998</v>
+        <v>-0.2670501521216195</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.2459161669571372</v>
+        <v>-0.246218916912099</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.2309065665762731</v>
+        <v>-0.2312167592940355</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.239290478036537</v>
+        <v>-0.2395967878080825</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.187848485088594</v>
+        <v>-0.1881681571183478</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.2730890111387225</v>
+        <v>-0.2733910366971912</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.1731428577807392</v>
+        <v>-0.1734700109461116</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.272272373947068</v>
+        <v>-0.2725810277142031</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.266599984815457</v>
+        <v>-0.266911570729448</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.2922237624647934</v>
+        <v>-0.2925289842871663</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.329710404067427</v>
+        <v>-0.3300093905111083</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.3614028111253873</v>
+        <v>-0.3610214135163616</v>
       </c>
     </row>
     <row r="7">
@@ -2266,49 +2266,49 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3927</v>
+        <v>3928</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.2853164927988061</v>
+        <v>-0.2860416331732765</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.4365681657205656</v>
+        <v>-0.4372797885728019</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.7670213203193228</v>
+        <v>-0.7676554326994989</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.6231200141483413</v>
+        <v>-0.6237890453133588</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.6397560393086579</v>
+        <v>-0.6404294088435307</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.5318266066291031</v>
+        <v>-0.5325232378189639</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.6790720727122945</v>
+        <v>-0.6797329514306441</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.7765589882929049</v>
+        <v>-0.7772025760775634</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.6711331458606935</v>
+        <v>-0.6718048342237282</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.7187774378230145</v>
+        <v>-0.7194503548125937</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.6549926268902198</v>
+        <v>-0.6556852720426889</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.6064523278626268</v>
+        <v>-0.6071571808246787</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.6306688617171901</v>
+        <v>-0.6313743589868466</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.6722554986570941</v>
+        <v>-0.6714178983366068</v>
       </c>
     </row>
     <row r="8">
@@ -2318,49 +2318,49 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3722</v>
+        <v>3723</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.4720193108391584</v>
+        <v>-0.4734213838534131</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.4628051843793699</v>
+        <v>-0.4642574114161206</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.7361517354043627</v>
+        <v>-0.7375430316526348</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.5914924589318105</v>
+        <v>-0.5929194603983987</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.633055422851946</v>
+        <v>-0.6344877570888556</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.5623494118656822</v>
+        <v>-0.5637927812836239</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.7130396168363617</v>
+        <v>-0.7144458292610665</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.6829101666680373</v>
+        <v>-0.6843388687522278</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.5951363437722819</v>
+        <v>-0.5965911422217545</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.6791240120414841</v>
+        <v>-0.6805819176485812</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.5737043095242385</v>
+        <v>-0.5751972836579711</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.6049213943950917</v>
+        <v>-0.6064057762103729</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.6879106017019581</v>
+        <v>-0.689385802167763</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.7992918048507249</v>
+        <v>-0.7977996733215207</v>
       </c>
     </row>
     <row r="9">
@@ -2370,49 +2370,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3522</v>
+        <v>3523</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.6688272876781554</v>
+        <v>-0.670961279403123</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.5396469077073363</v>
+        <v>-0.5418899595246316</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.6929177187405315</v>
+        <v>-0.6951361003170007</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.5191178808892545</v>
+        <v>-0.5213808867008964</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.532517711190458</v>
+        <v>-0.5348020175208106</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.5029580593073675</v>
+        <v>-0.5052387678629628</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.6006961266150057</v>
+        <v>-0.6029541341771889</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.4573084810724808</v>
+        <v>-0.4596290913350458</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.4460925420720372</v>
+        <v>-0.4484202858963826</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.42985997575434</v>
+        <v>-0.4322313689396253</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.3351398847539002</v>
+        <v>-0.3375485191240486</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.2281281058388487</v>
+        <v>-0.2305668500358706</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.3202487709895649</v>
+        <v>-0.3226813809883353</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.5372099983445366</v>
+        <v>-0.5351154621491503</v>
       </c>
     </row>
     <row r="10">
@@ -2422,49 +2422,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3283</v>
+        <v>3284</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.8854286114721077</v>
+        <v>-0.8885593426362632</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.8121439513836393</v>
+        <v>-0.8154030944719608</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.8872516173057363</v>
+        <v>-0.8905153899920677</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.9532898211627199</v>
+        <v>-0.956526931856537</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.8375748461723092</v>
+        <v>-0.8408838638064964</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.7971762163034839</v>
+        <v>-0.8004800486142827</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-1.199899772308832</v>
+        <v>-1.203088589636877</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-1.194752541497898</v>
+        <v>-1.197975110123359</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-1.178511621305788</v>
+        <v>-1.181744932264507</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-1.129931296091726</v>
+        <v>-1.133236544860935</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.9527784373065273</v>
+        <v>-0.9561527906479697</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.9928775862445676</v>
+        <v>-0.9962394002488963</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-1.183153165048026</v>
+        <v>-1.186486348706971</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-1.373431491442268</v>
+        <v>-1.370170847276221</v>
       </c>
     </row>
     <row r="11">
@@ -2477,46 +2477,46 @@
         <v>3045</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.791867639581703</v>
+        <v>-0.7962578689380209</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.5861903292462429</v>
+        <v>-0.5907932230746198</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.6360954400327756</v>
+        <v>-0.6407196621993734</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.9140100816801962</v>
+        <v>-0.9185344158454072</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.8451391547387743</v>
+        <v>-0.8497364766551811</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.8249627333890572</v>
+        <v>-0.8295429183696328</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-1.416651977201944</v>
+        <v>-1.42104841989412</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-1.341599007165939</v>
+        <v>-1.34606420275378</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-1.450557907490825</v>
+        <v>-1.454995431533519</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-1.396917760756601</v>
+        <v>-1.401451193212381</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-1.207841088356091</v>
+        <v>-1.194383794645873</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-1.38518788465224</v>
+        <v>-1.389739807042766</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-1.491859956597445</v>
+        <v>-1.49641698109059</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-1.603386571775999</v>
+        <v>-1.613816207474152</v>
       </c>
     </row>
     <row r="12">
@@ -2529,46 +2529,46 @@
         <v>2762</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.6469502680738444</v>
+        <v>-0.6344279783982216</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.6654753654696748</v>
+        <v>-0.6525655558936236</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.8793158316607617</v>
+        <v>-0.8663087002431595</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-1.292147420269764</v>
+        <v>-1.2791682778713</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-1.03404437755772</v>
+        <v>-1.020933573182781</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-1.315892809139669</v>
+        <v>-1.302849912845303</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-1.50924347065525</v>
+        <v>-1.496177216354774</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-1.469547796301342</v>
+        <v>-1.456366787006104</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-1.494342034402543</v>
+        <v>-1.481143295447779</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-1.692765553970666</v>
+        <v>-1.679360426317835</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-1.426845453233931</v>
+        <v>-1.413388159523713</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-1.790724424780613</v>
+        <v>-1.777272136060503</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-1.885128202995602</v>
+        <v>-1.871572156644</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-2.250902888098025</v>
+        <v>-2.261332523796177</v>
       </c>
     </row>
     <row r="13">
@@ -2581,46 +2581,46 @@
         <v>2419</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.007595164701143631</v>
+        <v>0.02011745437676637</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.07442077980507378</v>
+        <v>-0.06151097022902263</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.05589552195353775</v>
+        <v>-0.04288839053593563</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.1736787680149163</v>
+        <v>-0.1606996256164521</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.1333484328597123</v>
+        <v>-0.120237628484773</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.3733186489266132</v>
+        <v>-0.3602757526322478</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.5820705555333276</v>
+        <v>-0.5690043012328516</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.42916300764265</v>
+        <v>-0.4159819983474122</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.3248053080457041</v>
+        <v>-0.3116065690909409</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.2241243748429582</v>
+        <v>-0.2107192471901271</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.1085344546220171</v>
+        <v>0.1219917483322348</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.4771733347047302</v>
+        <v>-0.4637210459846202</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.6080521705359487</v>
+        <v>-0.5944961241843458</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-1.226458163600711</v>
+        <v>-1.236887799298863</v>
       </c>
     </row>
     <row r="14">
@@ -2633,46 +2633,46 @@
         <v>2143</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.04972546887075424</v>
+        <v>0.06224775854637699</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.1619414712050329</v>
+        <v>-0.1490316616289817</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.04351106440918073</v>
+        <v>-0.03050393299157861</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.08674206819831909</v>
+        <v>0.09972121059678329</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.1549470780444864</v>
+        <v>0.1680578824194257</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.1075736533952423</v>
+        <v>-0.09453075710087688</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.6589429282970087</v>
+        <v>-0.6458766739965327</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.4261729906342779</v>
+        <v>-0.4129919813390401</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.2071915422388813</v>
+        <v>-0.1939928032841181</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-0.1240456120078264</v>
+        <v>-0.1106404843549953</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.3244908443558785</v>
+        <v>0.3379481380660962</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.4344064462688237</v>
+        <v>-0.4209541575487137</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.7613339456878236</v>
+        <v>-0.7477778993362207</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-1.351556617144624</v>
+        <v>-1.361986252842776</v>
       </c>
     </row>
     <row r="15">
@@ -2685,46 +2685,46 @@
         <v>1878</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.009224086605783555</v>
+        <v>0.0217463762814063</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.05815357321682768</v>
+        <v>-0.04524376364077654</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.1867815982372818</v>
+        <v>-0.1737744668196797</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.2695210108906991</v>
+        <v>-0.2565418684922349</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.3819571354410272</v>
+        <v>-0.3688463310660879</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.5637484245624265</v>
+        <v>-0.5507055282680611</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.967970959726081</v>
+        <v>-0.954904705425605</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.9559211316705216</v>
+        <v>-0.9427401223752838</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.6441840636462217</v>
+        <v>-0.6309853246914585</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.6423390676304805</v>
+        <v>-0.6289339399776495</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.00487778909560177</v>
+        <v>0.01833508280581952</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.5464685530264859</v>
+        <v>-0.5330162643063758</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.647234346080019</v>
+        <v>-0.6336782997284161</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-1.515723876423536</v>
+        <v>-1.526153512121688</v>
       </c>
     </row>
     <row r="16">
@@ -2737,46 +2737,46 @@
         <v>1665</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.2392944125227601</v>
+        <v>0.2518167021983828</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.1110179391802362</v>
+        <v>-0.09810812960418502</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.2148340749438944</v>
+        <v>0.2278412063614965</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.4652073276715143</v>
+        <v>0.4781864700699785</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.4673266531398852</v>
+        <v>0.4804374575148245</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.5245283506153058</v>
+        <v>0.5375712469096712</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.07943427298265959</v>
+        <v>0.09250052728313563</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.03267129462157925</v>
+        <v>0.04585230391681705</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.5122119489798251</v>
+        <v>0.5254106879345883</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.6831077849729184</v>
+        <v>0.6965129126257494</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>1.139015121316</v>
+        <v>1.152472415026217</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>1.173398278661431</v>
+        <v>1.186850567381541</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>1.353744268317122</v>
+        <v>1.367300314668725</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.5223845195123289</v>
+        <v>0.5119548838141768</v>
       </c>
     </row>
     <row r="17">
@@ -2789,46 +2789,46 @@
         <v>1446</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.4111259951427257</v>
+        <v>0.4236482848183485</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.7163535652627502</v>
+        <v>-0.703443755686699</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.2813467531871439</v>
+        <v>-0.2683396217695417</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.151093620579644</v>
+        <v>-0.1381144781811798</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.1403606830203898</v>
+        <v>0.1534714873953291</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.2994900342906845</v>
+        <v>0.3125329305850499</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.1456000237957227</v>
+        <v>0.1586662780961987</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.3215833749857779</v>
+        <v>-0.3084023656905401</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.1015107913907016</v>
+        <v>0.1147095303454648</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.01210483181228739</v>
+        <v>0.02550995946511847</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.6372270261669044</v>
+        <v>0.6506843198771222</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.1875161309535542</v>
+        <v>0.2009684196736643</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.3896681590127997</v>
+        <v>0.4032242053644026</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.08613914550762303</v>
+        <v>0.07570950980947089</v>
       </c>
     </row>
     <row r="18">
@@ -2841,46 +2841,46 @@
         <v>1204</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.2474254671654421</v>
+        <v>0.2599477568410649</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.9488657537722318</v>
+        <v>-0.9359559441961807</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.6792826331263058</v>
+        <v>-0.6662755017087036</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.6137611971556112</v>
+        <v>0.6267403395540754</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.7397918093259719</v>
+        <v>0.7529026137009112</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.9541772686363146</v>
+        <v>0.96722016493068</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.7033305945534067</v>
+        <v>0.7163968488538828</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.01302223944404801</v>
+        <v>0.0001587698511897884</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.5073732232108625</v>
+        <v>0.5205719621656257</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.4047563438307833</v>
+        <v>0.4181614714836144</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>1.445850195592932</v>
+        <v>1.45930748930315</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.649668568885204</v>
+        <v>0.663120857605314</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1.059978741993461</v>
+        <v>1.073534788345064</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.7283047254325368</v>
+        <v>0.7178750897343846</v>
       </c>
     </row>
     <row r="19">
@@ -2893,46 +2893,46 @@
         <v>1029</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.4706044397511491</v>
+        <v>0.4831267294267718</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.3167567743087645</v>
+        <v>0.3296665838848156</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1.088068825729664</v>
+        <v>1.101075957147266</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>2.773229635693816</v>
+        <v>2.786208778092281</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>3.01226225929998</v>
+        <v>3.02537306367492</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>3.504067656685216</v>
+        <v>3.517110552979581</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>3.710879128917313</v>
+        <v>3.723945383217789</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>2.660605351127067</v>
+        <v>2.673786360422305</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>3.668604493127468</v>
+        <v>3.681803232082231</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>3.012842767769122</v>
+        <v>3.026247895421953</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>4.071451931303834</v>
+        <v>4.084909225014052</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>3.036836060466563</v>
+        <v>3.050288349186673</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>2.810944909191235</v>
+        <v>2.824500955542838</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>2.477575862458778</v>
+        <v>2.467146226760626</v>
       </c>
     </row>
     <row r="20">
@@ -2945,46 +2945,46 @@
         <v>939</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.009224086605783555</v>
+        <v>0.0217463762814063</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.4308905274234363</v>
+        <v>-0.4179807178473851</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.7716848554368454</v>
+        <v>0.7846919868544475</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>2.286389532240293</v>
+        <v>2.299368674638757</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>2.599938498211799</v>
+        <v>2.613049302586738</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>3.11037298118837</v>
+        <v>3.123415877482735</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>3.345128081807459</v>
+        <v>3.358194336107935</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1.812981956721387</v>
+        <v>1.826162966016625</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>2.816944796843657</v>
+        <v>2.83014353579842</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>2.392804702337571</v>
+        <v>2.406209829990402</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>3.678999194846398</v>
+        <v>3.692456488556616</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>2.43542708062634</v>
+        <v>2.44887936934645</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>2.547653832833717</v>
+        <v>2.56120987918532</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>2.477886347218636</v>
+        <v>2.467456711520484</v>
       </c>
     </row>
     <row r="21">
@@ -2997,46 +2997,46 @@
         <v>824</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.1876130774915268</v>
+        <v>-0.175090787815904</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.1001575642421884</v>
+        <v>-0.08724775466613721</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.9612844087728689</v>
+        <v>0.974291540190471</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>2.911925890894928</v>
+        <v>2.924905033293392</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>2.858941569026641</v>
+        <v>2.87205237340158</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>3.884538846548125</v>
+        <v>3.89758174284249</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>3.678445905974883</v>
+        <v>3.691512160275359</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.876311050882698</v>
+        <v>1.889492060177936</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>3.635699514214963</v>
+        <v>3.648898253169726</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>3.392370445691881</v>
+        <v>3.405775573344712</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>5.614801587393721</v>
+        <v>5.628258881103939</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>4.192874065127505</v>
+        <v>4.206326353847615</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>4.136697124085522</v>
+        <v>4.150253170437125</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>4.265059233060832</v>
+        <v>4.25462959736268</v>
       </c>
     </row>
     <row r="22">
@@ -3049,46 +3049,46 @@
         <v>655</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.3309891607060536</v>
+        <v>0.3435114503816763</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.3988048607189043</v>
+        <v>0.4117146702949555</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.3092796655726886</v>
+        <v>0.3222867969902907</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1.813578599706908</v>
+        <v>1.826557742105372</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>2.496531430436264</v>
+        <v>2.509642234811203</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>3.2519886353275</v>
+        <v>3.265031531621865</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>3.472598429505602</v>
+        <v>3.485664683806078</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>1.326025717747008</v>
+        <v>1.339206727042246</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>4.471132701793699</v>
+        <v>4.484331440748463</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>4.995053318292499</v>
+        <v>5.00845844594533</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>6.46968930695202</v>
+        <v>6.483146600662238</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>4.519339639869969</v>
+        <v>4.532791928590079</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>3.488398006024305</v>
+        <v>3.501954052375908</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>3.890791094025779</v>
+        <v>3.880361458327627</v>
       </c>
     </row>
     <row r="23">
@@ -3101,46 +3101,46 @@
         <v>534</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.8773481966439576</v>
+        <v>0.8898704863195803</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>1.887497430121648</v>
+        <v>1.900407239697699</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>2.054426476334051</v>
+        <v>2.067433607751653</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>3.308275114559521</v>
+        <v>3.321254256957985</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>3.893449405105329</v>
+        <v>3.906560209480268</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>4.752689095629982</v>
+        <v>4.765731991924348</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>4.855221295960703</v>
+        <v>4.868287550261179</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>2.515378721149233</v>
+        <v>2.528559730444471</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>4.888835763805886</v>
+        <v>4.90203450276065</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>5.911369754807914</v>
+        <v>5.924774882460746</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>7.766541524123298</v>
+        <v>7.779998817833516</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>5.740999587835766</v>
+        <v>5.754451876555876</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>4.009883553669901</v>
+        <v>4.023439600021504</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>3.885073050740196</v>
+        <v>3.874643415042044</v>
       </c>
     </row>
     <row r="24">
@@ -3153,46 +3153,46 @@
         <v>469</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1.237904963372117</v>
+        <v>1.250427253047739</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>2.824625593478224</v>
+        <v>2.837535403054275</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>3.282635351700392</v>
+        <v>3.295642483117994</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>4.692206181536037</v>
+        <v>4.705185323934501</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>5.646322279896708</v>
+        <v>5.659433084271647</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>6.583423066226437</v>
+        <v>6.596465962520803</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>6.285469732749469</v>
+        <v>6.298535987049945</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>3.04643132330699</v>
+        <v>3.059612332602228</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>5.544066831580977</v>
+        <v>5.557265570535741</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>6.399698576190573</v>
+        <v>6.413103703843404</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>8.5403610301246</v>
+        <v>8.553818323834818</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>7.082206874037183</v>
+        <v>7.095659162757293</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>5.169414949659455</v>
+        <v>5.182970996011058</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>4.566257817116977</v>
+        <v>4.555828181418825</v>
       </c>
     </row>
     <row r="25">
@@ -3205,46 +3205,46 @@
         <v>373</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>2.198250687832925</v>
+        <v>2.210772977508547</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>2.999545707576445</v>
+        <v>3.012455517152496</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>3.408966545215776</v>
+        <v>3.421973676633378</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>4.611605736804499</v>
+        <v>4.624584879202963</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>5.145570580713567</v>
+        <v>5.158681385088506</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>6.515398577410458</v>
+        <v>6.528441473704824</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>7.234954404374108</v>
+        <v>7.248020658674584</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>4.35490237288483</v>
+        <v>4.368083382180068</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>5.634385060429068</v>
+        <v>5.647583799383831</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>6.660935478618299</v>
+        <v>6.67434060627113</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>8.600954272263195</v>
+        <v>8.614411565973413</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>7.831047885372698</v>
+        <v>7.844500174092808</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>4.4617316122294</v>
+        <v>4.475287658581003</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>4.443356429760378</v>
+        <v>4.432926794062226</v>
       </c>
     </row>
     <row r="26">
@@ -3257,46 +3257,46 @@
         <v>306</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0.1209407647573499</v>
+        <v>0.1334630544329727</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>1.777341008002239</v>
+        <v>1.79025081757829</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>1.709269687026563</v>
+        <v>1.722276818444165</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>2.49311759087589</v>
+        <v>2.506096733274354</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>2.935088532666477</v>
+        <v>2.948199337041416</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>4.212922627244879</v>
+        <v>4.225965523539244</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>5.435378452456256</v>
+        <v>5.448444706756732</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>2.680613354328358</v>
+        <v>2.693794363623596</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>4.58039778187154</v>
+        <v>4.593596520826303</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>4.710664753706354</v>
+        <v>4.724069881359185</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>7.120290514356093</v>
+        <v>7.13374780806631</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>5.847484129217868</v>
+        <v>5.860936417937978</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>3.139647818926562</v>
+        <v>3.153203865278165</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>1.75538222309828</v>
+        <v>1.744952587400128</v>
       </c>
     </row>
     <row r="27">
@@ -3309,46 +3309,46 @@
         <v>268</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-1.000901006777134</v>
+        <v>-0.9883787171015115</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.3726000071242765</v>
+        <v>0.3855098167003277</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.7239999572441036</v>
+        <v>0.7370070886617057</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>1.227387418209808</v>
+        <v>1.240366560608273</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>1.062100531495844</v>
+        <v>1.075211335870783</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>2.105811125927929</v>
+        <v>2.118854022222294</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>3.886749050446696</v>
+        <v>3.899815304747172</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>0.4344910247995202</v>
+        <v>0.447672034094758</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>1.86602845205006</v>
+        <v>1.879227191004823</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>1.762171923738542</v>
+        <v>1.775577051391373</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>5.288761883003055</v>
+        <v>5.302219176713272</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>4.576876383632076</v>
+        <v>4.590328672352186</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>1.171547145821492</v>
+        <v>1.185103192173095</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>0.6749998213813697</v>
+        <v>0.6645701856832176</v>
       </c>
     </row>
     <row r="28">
@@ -3361,46 +3361,46 @@
         <v>239</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.1921830900844554</v>
+        <v>-0.1796608004088327</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>1.125113589838321</v>
+        <v>1.138023399414372</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>1.567064966923738</v>
+        <v>1.58007209834134</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>2.115728141372237</v>
+        <v>2.128707283770702</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.3220768007770616</v>
+        <v>0.3351876051520009</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>1.874748864015729</v>
+        <v>1.887791760310094</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>3.463655314107477</v>
+        <v>3.476721568407953</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>0.4860116642799426</v>
+        <v>0.4991926735751804</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>2.935472029143675</v>
+        <v>2.948670768098438</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>2.922166927797754</v>
+        <v>2.935572055450585</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>6.064693938208208</v>
+        <v>6.078151231918426</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>6.517487137394639</v>
+        <v>6.530939426114749</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>3.168362233562704</v>
+        <v>3.181918279914306</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>2.581263482156992</v>
+        <v>2.570833846458839</v>
       </c>
     </row>
     <row r="29">
@@ -3413,46 +3413,46 @@
         <v>217</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.04112389177158349</v>
+        <v>0.05364618144720623</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>1.194527237332686</v>
+        <v>1.207437046908737</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.3388290376485301</v>
+        <v>0.3518361690661322</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.4690821702560299</v>
+        <v>0.4820613126544941</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-1.912657017166367</v>
+        <v>-1.899546212791428</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>2.071420865249756</v>
+        <v>2.084463761544121</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>2.908346134152588</v>
+        <v>2.921412388453064</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>0.1370152699333076</v>
+        <v>0.1501962792285454</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>2.840992342276351</v>
+        <v>2.854191081231114</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>1.990867157248424</v>
+        <v>2.004272284901255</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>5.011920284543741</v>
+        <v>5.025377578253959</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>5.967962428064283</v>
+        <v>5.981414716784393</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>3.70438984476916</v>
+        <v>3.717945891120763</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>4.414940670133007</v>
+        <v>4.404511034434854</v>
       </c>
     </row>
     <row r="30">
@@ -3465,46 +3465,46 @@
         <v>190</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.1381406271584424</v>
+        <v>0.1506629168340652</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>1.684461751036288</v>
+        <v>1.697371560612339</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.2369614654923424</v>
+        <v>0.2499685969099446</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>1.419846177047198</v>
+        <v>1.432825319445662</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.6975224064460193</v>
+        <v>-0.68441160207108</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>3.284130057585436</v>
+        <v>3.297172953879802</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>3.199396340313157</v>
+        <v>3.212462594613633</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>1.153265573110595</v>
+        <v>1.166446582405833</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>3.19752884482304</v>
+        <v>3.210727583777803</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>2.873719449268783</v>
+        <v>2.887124576921615</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>4.247913493372266</v>
+        <v>4.261370787082484</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>4.808612440191382</v>
+        <v>4.822064728911492</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>1.756778881878063</v>
+        <v>1.770334928229666</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>2.532816003628021</v>
+        <v>2.522386367929869</v>
       </c>
     </row>
     <row r="31">
@@ -3517,46 +3517,46 @@
         <v>165</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.3722261989978506</v>
+        <v>-0.3597039093222278</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>2.258624430462127</v>
+        <v>2.271534240038179</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>1.257695117804943</v>
+        <v>1.270702249222545</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>1.387948250412443</v>
+        <v>1.400927392810907</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-2.786836601023367</v>
+        <v>-2.773725796648428</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>1.146968973055934</v>
+        <v>1.160011869350299</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>1.062235255783655</v>
+        <v>1.075301510084131</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-1.223129961179666</v>
+        <v>-1.209948951884428</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>1.140112576880448</v>
+        <v>1.153311315835211</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>0.8960479979131293</v>
+        <v>0.9094531255659604</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>3.721597703898581</v>
+        <v>3.735054997608799</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>3.755980861244012</v>
+        <v>3.769433149964122</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>0.3054232199960794</v>
+        <v>0.3189792663476823</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>1.161205158332976</v>
+        <v>1.150775522634824</v>
       </c>
     </row>
     <row r="32">
@@ -3569,46 +3569,46 @@
         <v>144</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.2843394575678033</v>
+        <v>0.2968617472434261</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.756099177936882</v>
+        <v>0.7690089875129331</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.3332139731041579</v>
+        <v>-0.3202068416865558</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.2029608404966581</v>
+        <v>-0.1899816980981939</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-5.602493166679935</v>
+        <v>-5.589382362304995</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-1.13838456229761</v>
+        <v>-1.125341666003244</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.5286738351254456</v>
+        <v>-0.5156075808249696</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-1.690301678351389</v>
+        <v>-1.677120669056151</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.3624126756447978</v>
+        <v>-0.3492139366900346</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.5180934162282824</v>
+        <v>-0.5046882885754513</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>2.74937548167636</v>
+        <v>2.762832775386578</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>3.478203083466234</v>
+        <v>3.491655372186344</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.4142737497008895</v>
+        <v>-0.4007177033492866</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0.5298920270198408</v>
+        <v>0.5194623913216887</v>
       </c>
     </row>
     <row r="33">
@@ -3621,46 +3621,46 @@
         <v>119</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.4477381503782638</v>
+        <v>0.4602604400538866</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>3.878181344136699</v>
+        <v>3.89109115371275</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>1.802640368632538</v>
+        <v>1.81564750005014</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>1.092557366786259</v>
+        <v>1.105536509184724</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-4.487880655008603</v>
+        <v>-4.474769850633663</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-1.669430313931592</v>
+        <v>-1.656387417637227</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-1.754164031203871</v>
+        <v>-1.741097776903395</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-3.06168356443915</v>
+        <v>-3.048502555143912</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.601675047260116</v>
+        <v>-0.5884763083053528</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-1.451800232288043</v>
+        <v>-1.438395104635212</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>2.545127115663291</v>
+        <v>2.558584409373509</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>3.419846407462501</v>
+        <v>3.433298696182611</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-1.202088875751308</v>
+        <v>-1.188532829399705</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.1120314090212418</v>
+        <v>-0.1224610447193939</v>
       </c>
     </row>
     <row r="34">
@@ -3673,46 +3673,46 @@
         <v>102</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.4477381503782638</v>
+        <v>0.4602604400538866</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>4.718517478590478</v>
+        <v>4.731427288166529</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>4.323648771993888</v>
+        <v>4.33665590341149</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>4.453901904601388</v>
+        <v>4.466881046999852</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.9864800947845112</v>
+        <v>-0.9733692904095719</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>2.252138313519382</v>
+        <v>2.265181209813747</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>1.187012439384361</v>
+        <v>1.200078693684837</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-1.24095527312263</v>
+        <v>-1.227774263827392</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>1.639221311283301</v>
+        <v>1.652420050238064</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.7890961262553731</v>
+        <v>0.8025012539082041</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>4.505911429388775</v>
+        <v>4.519368723098992</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>5.520686743596954</v>
+        <v>5.534139032317064</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>0.1984713483383231</v>
+        <v>0.212027394689926</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>1.428584837477366</v>
+        <v>1.418155201779214</v>
       </c>
     </row>
     <row r="35">
@@ -3725,46 +3725,46 @@
         <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>2.268466441694791</v>
+        <v>2.280988731370414</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>8.990226162063863</v>
+        <v>9.003135971639914</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>9.78583364594347</v>
+        <v>9.798840777361072</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>9.916086778550969</v>
+        <v>9.929065920949434</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>4.615760801574034</v>
+        <v>4.628871605948973</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>7.294155120242074</v>
+        <v>7.307198016536439</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>8.399897593445985</v>
+        <v>8.412963847746461</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>4.361285623235915</v>
+        <v>4.374466632531153</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>7.871714308482183</v>
+        <v>7.884913047436946</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>7.021589123454255</v>
+        <v>7.034994251107086</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>12.76921675151763</v>
+        <v>12.78267404522785</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>16.37502848029163</v>
+        <v>16.38848076901174</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>11.19286910744197</v>
+        <v>11.20642515379357</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>12.63306663019445</v>
+        <v>12.6226369944963</v>
       </c>
     </row>
   </sheetData>
@@ -3815,7 +3815,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that Realized VOL-30 is below threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that Realized VOL-30 is below threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -3911,46 +3911,46 @@
         <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>9.41132358455193</v>
+        <v>9.423845874227553</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>8.990226162063863</v>
+        <v>9.003135971639914</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>13.35726221737204</v>
+        <v>13.37026934878964</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>13.48751534997954</v>
+        <v>13.500494492378</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>12.94909413490737</v>
+        <v>12.96220493928231</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>16.8179646440516</v>
+        <v>16.83100754034596</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>16.73323092677932</v>
+        <v>16.7462971810798</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>19.83747609942639</v>
+        <v>19.85065710872163</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>18.5860000227679</v>
+        <v>18.59919876172266</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>22.49777959964473</v>
+        <v>22.51118472729756</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>21.10255008485096</v>
+        <v>21.11600737856118</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>23.51788562314879</v>
+        <v>23.5313379118689</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>25.47858339315625</v>
+        <v>25.49213943950785</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>25.72830472543254</v>
+        <v>25.71787508973438</v>
       </c>
     </row>
     <row r="7">
@@ -3963,46 +3963,46 @@
         <v>221</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>5.877602403771931</v>
+        <v>5.890124693447554</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>8.790915668635719</v>
+        <v>8.80382547821177</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>13.8259112154328</v>
+        <v>13.8389183468504</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>11.69372090912626</v>
+        <v>11.70670005152473</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>12.0602770696197</v>
+        <v>12.07338787399464</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>11.45274163176975</v>
+        <v>11.46578452806412</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>14.98791741675992</v>
+        <v>15.0009836710604</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>16.33068876910965</v>
+        <v>16.34386977840489</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>15.81720019514454</v>
+        <v>15.83039893409931</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>16.32454107346503</v>
+        <v>16.33794620111786</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>14.76232168579904</v>
+        <v>14.77577897950925</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>14.34421615536166</v>
+        <v>14.35766844408177</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>14.82893891998237</v>
+        <v>14.84249496633397</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>15.07866025225866</v>
+        <v>15.06823061656051</v>
       </c>
     </row>
     <row r="8">
@@ -4015,46 +4015,46 @@
         <v>426</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>4.548815200916785</v>
+        <v>4.561337490592408</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>4.58043407621544</v>
+        <v>4.593343885791491</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>6.532983209994441</v>
+        <v>6.545990341412043</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>5.489527422414142</v>
+        <v>5.502506564812606</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>5.890073343492205</v>
+        <v>5.903184147867144</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>5.952773497170305</v>
+        <v>5.965816393464671</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>7.745974052198505</v>
+        <v>7.759040306498981</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>7.278790653417005</v>
+        <v>7.291971662712243</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>7.217790767234703</v>
+        <v>7.230989506189466</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>7.776116286432121</v>
+        <v>7.789521414084952</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>6.632395825964309</v>
+        <v>6.645853119674527</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>7.13626255138486</v>
+        <v>7.14971484010497</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>7.88971686062775</v>
+        <v>7.903272906979353</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>8.608921760979143</v>
+        <v>8.598492125280991</v>
       </c>
     </row>
     <row r="9">
@@ -4067,46 +4067,46 @@
         <v>626</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>4.056082446563188</v>
+        <v>4.068604736238811</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>3.402975287273058</v>
+        <v>3.415885096849109</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>3.966573034350589</v>
+        <v>3.979580165768191</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>3.138359713283968</v>
+        <v>3.151338855682432</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>3.238916133994543</v>
+        <v>3.252026938369482</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>3.536358071710204</v>
+        <v>3.549400968004569</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>4.410090808112045</v>
+        <v>4.423157062412521</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>3.463674182493484</v>
+        <v>3.476855191788722</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>3.881907523148243</v>
+        <v>3.895106262103006</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>3.67075997390306</v>
+        <v>3.684165101555891</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>2.986773422748421</v>
+        <v>3.000230716458638</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>2.541923353256792</v>
+        <v>2.555375641976902</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>3.08013519598601</v>
+        <v>3.093691242337613</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>4.12857857299074</v>
+        <v>4.118148937292588</v>
       </c>
     </row>
     <row r="10">
@@ -4119,46 +4119,46 @@
         <v>865</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>3.575925841639737</v>
+        <v>3.58844813131536</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>3.351635465669695</v>
+        <v>3.364545275245746</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>3.419194504737845</v>
+        <v>3.432201636155447</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>3.780661510177715</v>
+        <v>3.79364065257618</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>3.357847231521738</v>
+        <v>3.370958035896678</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>3.539682232821207</v>
+        <v>3.552725129115572</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>5.30465949820789</v>
+        <v>5.317725752508366</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>5.184296908674945</v>
+        <v>5.197477917970183</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>5.470117831741199</v>
+        <v>5.483316570695962</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>5.198027328794197</v>
+        <v>5.211432456447028</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>4.415239322395692</v>
+        <v>4.42869661610591</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>4.680836352573486</v>
+        <v>4.694288641293596</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>5.416651105790436</v>
+        <v>5.430207152142039</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>6.013193247315286</v>
+        <v>6.002763611617134</v>
       </c>
     </row>
     <row r="11">
@@ -4168,49 +4168,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>2.348190639066047</v>
+        <v>2.36071292874167</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>1.822589876780519</v>
+        <v>1.83549968635657</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>1.789712120410172</v>
+        <v>1.802719251827774</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>2.643947153470158</v>
+        <v>2.656926295868622</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>2.467516888624232</v>
+        <v>2.480627692999171</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>2.674461088783332</v>
+        <v>2.687503985077697</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>4.490179860198843</v>
+        <v>4.503246114499319</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>4.203991936530464</v>
+        <v>4.217172945825702</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>4.776476213244088</v>
+        <v>4.789674952198851</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>4.559835191112086</v>
+        <v>4.573240318764917</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>3.957104950275387</v>
+        <v>3.916050472721921</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>4.534966368490387</v>
+        <v>4.548418657210497</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>4.839349438704907</v>
+        <v>4.85290548505651</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>5.054169250753091</v>
+        <v>5.078641135283043</v>
       </c>
     </row>
     <row r="12">
@@ -4220,49 +4220,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>1.402201422463364</v>
+        <v>1.376226826608509</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>1.474387208456669</v>
+        <v>1.447569070111612</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>1.763540977981506</v>
+        <v>1.736302457312021</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>2.650429799426931</v>
+        <v>2.622592866444876</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>2.152883177406082</v>
+        <v>2.125119388729701</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>2.921674420645161</v>
+        <v>2.893475538297828</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>3.452541766693173</v>
+        <v>3.423895049495457</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>3.31448759367926</v>
+        <v>3.28568941310067</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>3.583090160044954</v>
+        <v>3.554042768290806</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>3.92635102821616</v>
+        <v>3.896621720211193</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>3.332828805410458</v>
+        <v>3.303400321349812</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>4.13062063069647</v>
+        <v>4.100606656083627</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>4.330679386564427</v>
+        <v>4.300290942183857</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>4.985158982286798</v>
+        <v>5.002559403257919</v>
       </c>
     </row>
     <row r="13">
@@ -4272,49 +4272,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1729</v>
+        <v>1730</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.08979933765454717</v>
+        <v>0.07215339000494936</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.2315762345454715</v>
+        <v>0.2132939728426919</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.09782050965446842</v>
+        <v>0.07946767487480599</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.3169739879488063</v>
+        <v>0.2985240490282521</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.270317215624118</v>
+        <v>0.2516980798392723</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.7722371993604185</v>
+        <v>0.7534142475628016</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>1.180235535074246</v>
+        <v>1.161133927522762</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.918167742077685</v>
+        <v>0.8990442054958123</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.9471797887919493</v>
+        <v>0.928003482458216</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.7642044615687311</v>
+        <v>0.7448311270339261</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.2458471265313804</v>
+        <v>0.2266880039561769</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>1.121665436633961</v>
+        <v>1.101996660356733</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>1.312604863015878</v>
+        <v>1.292667623051635</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>2.11639032404446</v>
+        <v>2.129931241674932</v>
       </c>
     </row>
     <row r="14">
@@ -4324,49 +4324,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.03381638742134641</v>
+        <v>0.02032220621651959</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.282692578476734</v>
+        <v>0.2686510974127216</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.06361142372123396</v>
+        <v>0.0495667494554084</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.02719574537672287</v>
+        <v>-0.04117217428866837</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.0917627242215886</v>
+        <v>-0.1058560320044677</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.3322645517941254</v>
+        <v>0.3180269757268661</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>1.020365263615446</v>
+        <v>1.005753571683719</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.730066850296609</v>
+        <v>0.715468241922423</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.6471229794132398</v>
+        <v>0.6325391988423164</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.5216720834675286</v>
+        <v>0.5069203349734721</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.003501897695038281</v>
+        <v>-0.01805600288896159</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.8561303380750971</v>
+        <v>0.8411462973744861</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>1.212097137637102</v>
+        <v>1.19681592893771</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>1.789936360630264</v>
+        <v>1.80034197479349</v>
       </c>
     </row>
     <row r="15">
@@ -4376,49 +4376,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2270</v>
+        <v>2271</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.06897955101210584</v>
+        <v>0.05848852288070816</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.1456453849677501</v>
+        <v>0.1347923135459297</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.1691241826754748</v>
+        <v>0.1581746949771983</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.2794952998542257</v>
+        <v>0.268516036813395</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.3793580351142225</v>
+        <v>0.368219976876297</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.6571719687725306</v>
+        <v>0.6459639748723873</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>1.079802229872364</v>
+        <v>1.068384224852529</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>1.032555185542385</v>
+        <v>1.021056757382148</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.9083443451122193</v>
+        <v>0.896880576100429</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.8744600871431629</v>
+        <v>0.8628330789459113</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.2988084386104148</v>
+        <v>0.2873856924197042</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.7982343823707723</v>
+        <v>0.7865910910111893</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.8874655721837428</v>
+        <v>0.8756907473549376</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>1.559015864513725</v>
+        <v>1.56709192309917</v>
       </c>
     </row>
     <row r="16">
@@ -4428,49 +4428,49 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2483</v>
+        <v>2484</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.08959216636382195</v>
+        <v>-0.09805659921676835</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.163525140974059</v>
+        <v>0.1546927481966875</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.1293914657531801</v>
+        <v>-0.1381761135636381</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.2581152729074034</v>
+        <v>-0.2668328074272495</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.2531530561038693</v>
+        <v>-0.2619655953575517</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.1746372943552359</v>
+        <v>-0.1834386875834184</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.2042578917821913</v>
+        <v>0.1952849656757678</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.2010759387192778</v>
+        <v>0.1920225705690157</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.001556599096176114</v>
+        <v>-0.007432319797935349</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.1428086018602315</v>
+        <v>-0.1518837155136481</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.4859646452566935</v>
+        <v>-0.4949409814824719</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.4693712514320438</v>
+        <v>-0.4783544606553463</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.5853687577524127</v>
+        <v>-0.5943796751802708</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.07141911094051068</v>
+        <v>-0.06427351850118157</v>
       </c>
     </row>
     <row r="17">
@@ -4480,49 +4480,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2702</v>
+        <v>2703</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.1545801249981835</v>
+        <v>-0.1613284016683707</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.4638900565088946</v>
+        <v>0.4567008229948186</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.1628543399564109</v>
+        <v>0.1557204489054342</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.1288975665829923</v>
+        <v>0.1217887896767138</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.02055333308020124</v>
+        <v>-0.02768128069241271</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.001939340941426337</v>
+        <v>-0.005162560302188979</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.1588492361185558</v>
+        <v>0.1516740919917652</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.3766193785992087</v>
+        <v>0.3692986738748232</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.2622538268384744</v>
+        <v>0.2549629876493711</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.2825964088517878</v>
+        <v>0.2751828274611654</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.0861656972104754</v>
+        <v>-0.09347419677404645</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.1908921038475597</v>
+        <v>0.1834812091138431</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.08748355699537314</v>
+        <v>0.08005152741993982</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.2101700104066282</v>
+        <v>0.2157874622305513</v>
       </c>
     </row>
     <row r="18">
@@ -4532,49 +4532,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2944</v>
+        <v>2945</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.04162905406185757</v>
+        <v>-0.04683895142684236</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.4619704754861118</v>
+        <v>0.45642679084213</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.2886134380633578</v>
+        <v>0.2830858962475915</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.2057818741233817</v>
+        <v>-0.2111322903147723</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.2517669748599474</v>
+        <v>-0.2571586355315034</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.2406880853328417</v>
+        <v>-0.2460569461326827</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.06978984099915664</v>
+        <v>-0.07522817703092954</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.1934083028162235</v>
+        <v>0.1878309480981102</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.08335990263032045</v>
+        <v>0.0778105454191973</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.1000280974156169</v>
+        <v>0.09438484355973742</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.3571264223314827</v>
+        <v>-0.3626383538158962</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.001737819831923559</v>
+        <v>-0.003895658994146345</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.1617270603969914</v>
+        <v>-0.1673504256846527</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.06265024351155546</v>
+        <v>-0.05825879336044437</v>
       </c>
     </row>
     <row r="19">
@@ -4584,49 +4584,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3119</v>
+        <v>3120</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.09880230488430897</v>
+        <v>-0.1030034866466991</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.03283052148467647</v>
+        <v>-0.03718513764670917</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.3465260071829661</v>
+        <v>-0.3508147411861842</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.8701068935487513</v>
+        <v>-0.8742202497488805</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.943854348833959</v>
+        <v>-0.9479900111810977</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-1.012909310902941</v>
+        <v>-1.017001228378923</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-1.016517725080654</v>
+        <v>-1.020617707677118</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.6985239005736119</v>
+        <v>-0.7027657959488778</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.9341511875241579</v>
+        <v>-0.9383250478011504</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.7422368680374376</v>
+        <v>-0.746543460008084</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-1.121451623455677</v>
+        <v>-1.125655857338359</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.748985495692871</v>
+        <v>-0.7533086821947492</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.670684006111145</v>
+        <v>-0.6750688728462393</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.5953796056259435</v>
+        <v>-0.5916487197894185</v>
       </c>
     </row>
     <row r="20">
@@ -4636,49 +4636,49 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3209</v>
+        <v>3210</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.05156478345234916</v>
+        <v>0.04778393843864848</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.1948949280489884</v>
+        <v>0.1909518801262138</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.2141663540565375</v>
+        <v>-0.2180129060557974</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.626228936178542</v>
+        <v>-0.6299402902306994</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.7128964537457492</v>
+        <v>-0.7166216705787889</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.7716263679826909</v>
+        <v>-0.775314043601476</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.7774300540309156</v>
+        <v>-0.7811241076097559</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.3569251447415667</v>
+        <v>-0.3607856773480265</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.556442268398726</v>
+        <v>-0.5602472873034898</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.4558462951576345</v>
+        <v>-0.4597460221023795</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.8612167419295673</v>
+        <v>-0.8650072495122743</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.4670026329945429</v>
+        <v>-0.4709155424393643</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.4960494506354749</v>
+        <v>-0.4999858441154075</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.5092859792818842</v>
+        <v>-0.5059789378579538</v>
       </c>
     </row>
     <row r="21">
@@ -4688,49 +4688,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3324</v>
+        <v>3325</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.09871031628987481</v>
+        <v>0.09547701919602503</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.09163075267708365</v>
+        <v>0.08829943468770551</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.2270170715549327</v>
+        <v>-0.2302787841326008</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.6803653595928409</v>
+        <v>-0.683484946473996</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.6626241797812469</v>
+        <v>-0.6657837486943805</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.8290941794778135</v>
+        <v>-0.8321873505717008</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.7175560526777218</v>
+        <v>-0.7206896136380934</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.2976590357087545</v>
+        <v>-0.3009490155653722</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.6425685449415539</v>
+        <v>-0.645760483236586</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.6048989717838396</v>
+        <v>-0.6081561301027634</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-1.183722404307012</v>
+        <v>-1.186820002391201</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.8020467996098688</v>
+        <v>-0.8052587646736882</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.7845745015805932</v>
+        <v>-0.7878193269211451</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.8489687832489068</v>
+        <v>-0.8460346847017064</v>
       </c>
     </row>
     <row r="22">
@@ -4740,49 +4740,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3493</v>
+        <v>3494</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.01197796653056571</v>
+        <v>-0.01442045026631433</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.01086072062073384</v>
+        <v>-0.01337993306766805</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.04782584525028</v>
+        <v>-0.05035425015065442</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.3016857429612116</v>
+        <v>-0.3041369492397408</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.424896237940807</v>
+        <v>-0.4273387171754308</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.483214610855164</v>
+        <v>-0.48562785167492</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.4667690732206822</v>
+        <v>-0.4691922709135099</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.0896459354407142</v>
+        <v>-0.09220003413551581</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.5923059479909014</v>
+        <v>-0.5947205893844583</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.711910338669739</v>
+        <v>-0.714331894445472</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-1.015244401364569</v>
+        <v>-1.017590126783531</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.6217015421894558</v>
+        <v>-0.6241595273814156</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.4250064343030644</v>
+        <v>-0.4275417376840451</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.531357456073323</v>
+        <v>-0.5291606449945334</v>
       </c>
     </row>
     <row r="23">
@@ -4792,49 +4792,49 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3614</v>
+        <v>3615</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.08097623032853818</v>
+        <v>-0.08290059503269731</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.2164294731631955</v>
+        <v>-0.2183772821314065</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.292984088046687</v>
+        <v>-0.2949264592633156</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.4513052113575782</v>
+        <v>-0.4532000889027969</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.5332212312059568</v>
+        <v>-0.5351145183020591</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.57968464205711</v>
+        <v>-0.5815550557661808</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.5390300903035694</v>
+        <v>-0.5409158819477327</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.2177725193581352</v>
+        <v>-0.2197654264896372</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.48464564362245</v>
+        <v>-0.4865681417238008</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.6562913156202157</v>
+        <v>-0.6581990803841151</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.9563121661594849</v>
+        <v>-0.9581456657411209</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.6300810856586452</v>
+        <v>-0.6320045055514996</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.3710510664367135</v>
+        <v>-0.3730628360926573</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.3824550184207283</v>
+        <v>-0.380722025460237</v>
       </c>
     </row>
     <row r="24">
@@ -4844,49 +4844,49 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3679</v>
+        <v>3680</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.1099063592132197</v>
+        <v>-0.1115686165078174</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.2984554444178045</v>
+        <v>-0.3001194583760736</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.4077397183616043</v>
+        <v>-0.4093877321408144</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.5610072848808585</v>
+        <v>-0.5626104243854542</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.6781137981573977</v>
+        <v>-0.6797034369714225</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.7185536247693562</v>
+        <v>-0.7201235411538818</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.6258885213254786</v>
+        <v>-0.6274871577167502</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.2371507662452501</v>
+        <v>-0.2388708348486333</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.4732523426733906</v>
+        <v>-0.4749112079096918</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.6025656158240267</v>
+        <v>-0.6042177854990811</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.9008900744827315</v>
+        <v>-0.902468760197344</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.6884635832004307</v>
+        <v>-0.6900997126105679</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.4414476627443662</v>
+        <v>-0.4431654077774283</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.3938946299823627</v>
+        <v>-0.3923733574705821</v>
       </c>
     </row>
     <row r="25">
@@ -4896,49 +4896,49 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3775</v>
+        <v>3776</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.1703126602310974</v>
+        <v>-0.1715995882012891</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.2365144417562206</v>
+        <v>-0.237825460451397</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.3266106978796444</v>
+        <v>-0.327908628501099</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.4198256577577766</v>
+        <v>-0.4210963309560967</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.468302422024081</v>
+        <v>-0.4695746417707198</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.5265465148925514</v>
+        <v>-0.5277964463650022</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.5440977730771479</v>
+        <v>-0.5453458837591469</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.2828624353527687</v>
+        <v>-0.2841921773703859</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.3293438925760199</v>
+        <v>-0.330663582580307</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.4504682361394856</v>
+        <v>-0.451778235665401</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.6669676746085713</v>
+        <v>-0.6682262937381225</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.5649087336725884</v>
+        <v>-0.5661941660761158</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.2288923937686889</v>
+        <v>-0.2302782010988267</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.2556120200736061</v>
+        <v>-0.2544312056651279</v>
       </c>
     </row>
     <row r="26">
@@ -4948,49 +4948,49 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3842</v>
+        <v>3843</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0.03574455916746189</v>
+        <v>0.03464413544075029</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.08321639606992193</v>
+        <v>-0.084320022430866</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.1266649636742656</v>
+        <v>-0.1277660874917785</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.1640200305278157</v>
+        <v>-0.1651093042924998</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.1949871797789839</v>
+        <v>-0.1960801816196422</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.2209963949094416</v>
+        <v>-0.2220770017024805</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.2656184960763355</v>
+        <v>-0.2666898319072146</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.06896880701852126</v>
+        <v>-0.07010152988579677</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.1416418007928257</v>
+        <v>-0.142757480233584</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.1714128823402632</v>
+        <v>-0.1725391391661049</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.387635065932372</v>
+        <v>-0.388709952989224</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.2606684623772111</v>
+        <v>-0.2617762128447225</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.041843356778692</v>
+        <v>-0.04301739117447312</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>0.04041895165401144</v>
+        <v>0.04132031481896092</v>
       </c>
     </row>
     <row r="27">
@@ -5000,49 +5000,49 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3880</v>
+        <v>3881</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.1138054506608199</v>
+        <v>0.1128179191317997</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.03167871430778035</v>
+        <v>0.03068236137485059</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.04087267266725547</v>
+        <v>-0.04185809211477931</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.05086144032527784</v>
+        <v>-0.05184240228734893</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.0353307998904171</v>
+        <v>-0.03632609266774978</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.0324174841083007</v>
+        <v>-0.03340857837716982</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.1031099898291501</v>
+        <v>-0.1040849470801035</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>0.1128235003527891</v>
+        <v>0.1117839417548154</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0.09179152855940487</v>
+        <v>0.09075575508099121</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.07980107970946193</v>
+        <v>0.07875229486513291</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.1877507380277592</v>
+        <v>-0.1887349097032498</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-0.1131587575092041</v>
+        <v>-0.1141620084185675</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>0.125213495854382</v>
+        <v>0.1241406171040822</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>0.1318393351527192</v>
+        <v>0.1326061973281654</v>
       </c>
     </row>
     <row r="28">
@@ -5052,49 +5052,49 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3909</v>
+        <v>3910</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.05628121064162883</v>
+        <v>0.05540821111744521</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.01166839836168521</v>
+        <v>-0.01255087423561463</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.08661533364837481</v>
+        <v>-0.08748559710608816</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.09557800473923095</v>
+        <v>-0.09644428313220033</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.01793392197073729</v>
+        <v>0.01702942074622626</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.002488326516257189</v>
+        <v>-0.003383183784421817</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.04774091037229766</v>
+        <v>-0.04862604733845899</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>0.1120610291837281</v>
+        <v>0.1111269759330611</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0.03963410798093747</v>
+        <v>0.03871709779272692</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.02141875119086478</v>
+        <v>0.02049197600184272</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.1945577153243221</v>
+        <v>-0.1954331189258269</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.1969723476539684</v>
+        <v>-0.1978470136350623</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>0.01091806615588098</v>
+        <v>0.009982884735599384</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>0.01931813770458035</v>
+        <v>0.02003073460102911</v>
       </c>
     </row>
     <row r="29">
@@ -5104,49 +5104,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3931</v>
+        <v>3932</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.04205863719367642</v>
+        <v>0.04126394411711232</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.009145841365970853</v>
+        <v>-0.009952022178303821</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.009774094869761996</v>
+        <v>-0.01058641730579524</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.007434152313969378</v>
+        <v>0.006619012201149133</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.1427126990842993</v>
+        <v>0.1418547743495466</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.002838315365224275</v>
+        <v>-0.003655258783844317</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0.002475648538002417</v>
+        <v>0.001655683963058152</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>0.1333866912475727</v>
+        <v>0.1325260777414385</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0.06102905877254727</v>
+        <v>0.06018549321993305</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.08899397611958904</v>
+        <v>0.08813013960883609</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.1014831298584085</v>
+        <v>-0.1023020544877724</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.1290941451124539</v>
+        <v>-0.129905945104511</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.0009980630274384339</v>
+        <v>-0.001849155167235494</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.067566917551801</v>
+        <v>-0.06689456583892905</v>
       </c>
     </row>
     <row r="30">
@@ -5156,49 +5156,49 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3958</v>
+        <v>3959</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.0374103325223345</v>
+        <v>0.0367073330104688</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.02440739916919199</v>
+        <v>-0.02511647766516489</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.002526142416321875</v>
+        <v>-0.003246304322992444</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.03495008780848252</v>
+        <v>-0.03566071044387087</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.07052450690490986</v>
+        <v>0.06977982407493499</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.0468145505309252</v>
+        <v>-0.04752607627689542</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>0.008316496946861207</v>
+        <v>0.007589595170998109</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>0.08470112465343504</v>
+        <v>0.08394840758669631</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0.06287540577499584</v>
+        <v>0.06212702081641197</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.05961705547512963</v>
+        <v>0.05885784650740078</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.02998018047404827</v>
+        <v>-0.03071986357241485</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.03189792663477675</v>
+        <v>-0.03263703433277243</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>0.1177419108194471</v>
+        <v>0.1169590643274816</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>0.05336066999328182</v>
+        <v>0.05392676223465287</v>
       </c>
     </row>
     <row r="31">
@@ -5208,49 +5208,49 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3983</v>
+        <v>3984</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.05911423234257995</v>
+        <v>0.05848852288070816</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.0374274525734819</v>
+        <v>-0.03804806954412498</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.04319561222951762</v>
+        <v>-0.0438196910816302</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.02452357528253657</v>
+        <v>-0.02515111889606203</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.1520715182454637</v>
+        <v>0.1513931615283823</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.06240749761497</v>
+        <v>0.06175474904907929</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>0.1166895733958597</v>
+        <v>0.1160219188827014</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>0.1896947005795582</v>
+        <v>0.1890029733832819</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0.1676497338057743</v>
+        <v>0.1669624929358804</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>0.1591074867062545</v>
+        <v>0.158412123772699</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>0.01863734263416461</v>
+        <v>0.01797448594589213</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>0.04205363414237695</v>
+        <v>0.04138498137405833</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>0.1881358888533242</v>
+        <v>0.1874253330371616</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>0.1257438416765737</v>
+        <v>0.1262227661543562</v>
       </c>
     </row>
     <row r="32">
@@ -5260,49 +5260,49 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4004</v>
+        <v>4005</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.03332294441536732</v>
+        <v>0.03277237165578839</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.02845420228393181</v>
+        <v>0.02788791872195873</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.02066730543465667</v>
+        <v>0.02009860320056589</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.03993901002650802</v>
+        <v>0.03936657919528841</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.2377275050259087</v>
+        <v>0.2370999496033264</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.1501110619407839</v>
+        <v>0.1495081277227044</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.1787557335606635</v>
+        <v>0.1781444962770564</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>0.199072109401456</v>
+        <v>0.1984506764104808</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0.2267131800687281</v>
+        <v>0.2260839297549566</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.2137761779167562</v>
+        <v>0.2131410398799716</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>0.07298278001537994</v>
+        <v>0.07238034691019379</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.07150757117910445</v>
+        <v>0.0709055732234134</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.2146276235825084</v>
+        <v>0.2139852422323401</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0.1538791510069615</v>
+        <v>0.1542938519958454</v>
       </c>
     </row>
     <row r="33">
@@ -5312,49 +5312,49 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4029</v>
+        <v>4030</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.03006489601961704</v>
+        <v>0.02959596550818588</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.05898372233532712</v>
+        <v>-0.05944502315285405</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.04443509521636457</v>
+        <v>-0.04490369890011436</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.0002660308411321921</v>
+        <v>-0.0002127212004978674</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.1687219563182509</v>
+        <v>0.168196521357082</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.1577855860523769</v>
+        <v>0.1572652351029191</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.2105068718451548</v>
+        <v>0.2099724703681574</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>0.2278106719170978</v>
+        <v>0.2272676141725682</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0.2301202390249486</v>
+        <v>0.2295758196090176</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>0.2367899074623736</v>
+        <v>0.2362360765432641</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>0.09560564040652508</v>
+        <v>0.09508475213396395</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.09435843504703456</v>
+        <v>0.09383791186888857</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>0.2339892775943895</v>
+        <v>0.2334301507811958</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>0.1751720799692862</v>
+        <v>0.1755142247928845</v>
       </c>
     </row>
     <row r="34">
@@ -5364,49 +5364,49 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4046</v>
+        <v>4047</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.03181420504255783</v>
+        <v>0.0313992404016048</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.06361222888640583</v>
+        <v>-0.0640163881953697</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.1000778298127258</v>
+        <v>-0.1004762683335088</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.07968667876095026</v>
+        <v>-0.08008933099606708</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.06112513719730117</v>
+        <v>0.06068338391459349</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.05145537630897223</v>
+        <v>0.05101810930844408</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.1282469642823969</v>
+        <v>0.1277898866968172</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>0.1681769878765351</v>
+        <v>0.1677062081541436</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.1702061564679767</v>
+        <v>0.1697341822087211</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.1732646084630787</v>
+        <v>0.1727850376265749</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.05649520945550535</v>
+        <v>0.0560426519297863</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.05538797586852695</v>
+        <v>0.05493574319701366</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>0.1926573103435913</v>
+        <v>0.1921676721447838</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>0.1351262775828062</v>
+        <v>0.1354330691900714</v>
       </c>
     </row>
     <row r="35">
@@ -5416,49 +5416,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4064</v>
+        <v>4065</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.003862651826359809</v>
+        <v>-0.004211763736904572</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.1305271441653986</v>
+        <v>-0.1308561093720328</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.193132173513149</v>
+        <v>-0.1934485819547973</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.1722784644534556</v>
+        <v>-0.1725992850102571</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.05904307529220887</v>
+        <v>-0.05939545345210462</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.04282682381255398</v>
+        <v>-0.04318136919771831</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.0159005607456848</v>
+        <v>-0.01626245967237594</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>0.04632130827160097</v>
+        <v>0.04594082279678702</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0.04804170845175548</v>
+        <v>0.04766021018410527</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0.04729498101852414</v>
+        <v>0.04690779017717261</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.09448294522854184</v>
+        <v>-0.09483684113259727</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.1446585878460027</v>
+        <v>-0.1450000932126656</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.03450745203791428</v>
+        <v>-0.03487904127354113</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.09073351978680222</v>
+        <v>-0.09041870748929171</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/btc_daily_14days/volatility/realized_vol_30.xlsx
+++ b/workspaces/btc_daily_14days/volatility/realized_vol_30.xlsx
@@ -575,46 +575,46 @@
         <v>137</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>3.710681881891574</v>
+        <v>3.681621719576313</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>8.654780473844326</v>
+        <v>8.653673187326014</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>14.08607059320645</v>
+        <v>14.0860315781609</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>10.57929542148309</v>
+        <v>10.57888066318816</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>11.50153716355566</v>
+        <v>11.55004564809995</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>8.159053545350616</v>
+        <v>8.183010019574354</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>13.90574798929573</v>
+        <v>13.95374303477678</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>14.17165806320124</v>
+        <v>14.22089127703345</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>14.11455324332009</v>
+        <v>14.18776620548476</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>12.53984756237682</v>
+        <v>12.63912843239653</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>10.87982637641217</v>
+        <v>10.97968055773472</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>8.7283436872412</v>
+        <v>8.851988999789377</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>8.310586201990603</v>
+        <v>8.459243323475484</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>8.538521596512275</v>
+        <v>8.710520356078611</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>205</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>3.116957448691025</v>
+        <v>3.087907026651202</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.05266016189390399</v>
+        <v>0.05148595588808291</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-1.31452601366292</v>
+        <v>-1.314677391285883</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-1.18441082403735</v>
+        <v>-1.184903694941795</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.748335601441859</v>
+        <v>-0.6999103070238206</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.03536217837093147</v>
+        <v>0.05927187178505733</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.04931322380809888</v>
+        <v>-0.00139006581819956</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-2.463698099844422</v>
+        <v>-2.414539088397234</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-2.037758860191097</v>
+        <v>-1.964608839773895</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-1.425339094137392</v>
+        <v>-1.326104930986617</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-2.117425665975929</v>
+        <v>-2.017604939598357</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.6208034216982696</v>
+        <v>-0.4971763512198848</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.4221700457084694</v>
+        <v>0.5708185529580234</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>1.623798434682122</v>
+        <v>1.795797194249005</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>200</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>3.006243876254622</v>
+        <v>2.977213022304092</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.9032399235154003</v>
+        <v>0.902076704988616</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-1.484541127129852</v>
+        <v>-1.484694498411088</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-1.853071436079752</v>
+        <v>-1.853570550029502</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-2.390452059580014</v>
+        <v>-2.342053671264836</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-1.595221727688511</v>
+        <v>-1.571328553636775</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-2.678372038163545</v>
+        <v>-2.630474808952741</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-4.642601597955952</v>
+        <v>-4.593465219213485</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-3.206620776393294</v>
+        <v>-3.133488822913698</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-5.055276833156967</v>
+        <v>-4.956068708811827</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-4.761380270922949</v>
+        <v>-4.661576964915504</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-7.226808460774244</v>
+        <v>-7.103201025368413</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-7.148884181243361</v>
+        <v>-7.000246961961587</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-5.424982053122754</v>
+        <v>-5.252983293556092</v>
       </c>
     </row>
     <row r="9">
@@ -731,98 +731,98 @@
         <v>239</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>2.318963572720875</v>
+        <v>2.289951268488224</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>3.216340731550765</v>
+        <v>3.215210827352308</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>1.989489787937956</v>
+        <v>1.989374099744275</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>5.457780671002375</v>
+        <v>5.457353446241974</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>3.670941845249956</v>
+        <v>3.719373939732073</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>3.551549374343374</v>
+        <v>3.575474723004064</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>7.64324482703465</v>
+        <v>7.691198394709609</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>9.685677710760523</v>
+        <v>9.734883534918971</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>9.627889917756036</v>
+        <v>9.701068707625119</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>9.199990378866232</v>
+        <v>9.299235660910369</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>8.162436533949403</v>
+        <v>8.262263687607415</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>10.29022250100848</v>
+        <v>10.41385197769772</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>11.54650487000748</v>
+        <v>11.69515330083284</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>10.93903468327883</v>
+        <v>11.11103344284559</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ 33</t>
+          <t>X ≈ 33.01</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-2.064534185360678</v>
+        <v>-1.486856289999828</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-3.677064426710096</v>
+        <v>-3.279221768203044</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-4.073059285928387</v>
+        <v>-3.867271165623244</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-1.440573840868552</v>
+        <v>-1.43888641309448</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.7280963904833442</v>
+        <v>-0.6802291119553132</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.4302020636559263</v>
+        <v>-0.4079776605514738</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>1.573847323054771</v>
+        <v>1.609272760917314</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.6887666767368614</v>
+        <v>0.7294342013186395</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>2.299626491476722</v>
+        <v>2.35711407821946</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>2.283975188319573</v>
+        <v>2.367822434470355</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>2.079049749827441</v>
+        <v>2.165207708277663</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>4.017186284635336</v>
+        <v>3.88991117504839</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>2.762211457184613</v>
+        <v>2.663366410161672</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>1.734013762776918</v>
+        <v>1.247016706443901</v>
       </c>
     </row>
     <row r="11">
@@ -832,49 +832,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-2.375671853640959</v>
+        <v>-2.396810152921724</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.01208728309524787</v>
+        <v>-0.2869651734817822</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>1.560965578355173</v>
+        <v>1.354829578767813</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>2.601150131559258</v>
+        <v>2.521966764312651</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.8210987905153075</v>
+        <v>0.1507564348800301</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>3.78979955068268</v>
+        <v>3.344805392464266</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.6878126042604578</v>
+        <v>-1.297756280924702</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.2695421613935665</v>
+        <v>-0.9104831987392075</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-1.199799671352643</v>
+        <v>-2.127855151655474</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>1.310864360982919</v>
+        <v>-0.05001083155090669</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.9430368972007273</v>
+        <v>-0.4135475590774291</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>2.392466174395338</v>
+        <v>0.8576748591412553</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>2.164991481377719</v>
+        <v>0.3069349093106979</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>4.705759996347211</v>
+        <v>2.791385307126504</v>
       </c>
     </row>
     <row r="12">
@@ -887,46 +887,46 @@
         <v>343</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-5.250595330825895</v>
+        <v>-5.279791125178527</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-4.820965097359114</v>
+        <v>-4.82215188380377</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-6.673462429636018</v>
+        <v>-6.673615819640339</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-9.167143991587018</v>
+        <v>-9.167638483965021</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-7.373072028647726</v>
+        <v>-7.324526108881955</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-7.95033356752576</v>
+        <v>-7.926376158576147</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-8.035043926791928</v>
+        <v>-7.987032247801608</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-8.793657760083036</v>
+        <v>-8.744410197689319</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-9.729275485118933</v>
+        <v>-9.656018375339237</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-12.03692022897073</v>
+        <v>-11.93757290367616</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-12.24162138723085</v>
+        <v>-12.14171335121218</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-11.0410624768581</v>
+        <v>-10.91736585582986</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-10.87812295116269</v>
+        <v>-10.72943340338487</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-9.486206542918673</v>
+        <v>-9.31420778335201</v>
       </c>
     </row>
     <row r="13">
@@ -939,46 +939,46 @@
         <v>276</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.3070029870560944</v>
+        <v>-0.3361987814087257</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.618042803938053</v>
+        <v>0.6168560174933972</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.1390474213967039</v>
+        <v>-0.1392008114010252</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-2.1827353212866</v>
+        <v>-2.183229813664603</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-2.358706033802584</v>
+        <v>-2.310160114036812</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-2.423650844747208</v>
+        <v>-2.399693435797595</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.02787068004460025</v>
+        <v>0.07588235903492091</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.4391979637420533</v>
+        <v>-0.3899504013483366</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-1.224817801424344</v>
+        <v>-1.151560691644647</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.9877800760150635</v>
+        <v>-0.8884327507204901</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-1.554800074854882</v>
+        <v>-1.454892038836206</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.7957842413401437</v>
+        <v>-0.6720876203118991</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.5956591082449165</v>
+        <v>0.7443486560227441</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.2655617632676766</v>
+        <v>-0.09356300370101422</v>
       </c>
     </row>
     <row r="14">
@@ -991,46 +991,46 @@
         <v>265</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.3492726487109294</v>
+        <v>0.3200768543582981</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.8845549537868607</v>
+        <v>-0.8857417402315164</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.9848246048543672</v>
+        <v>0.9846712148500458</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>2.624483710706883</v>
+        <v>2.62398921832888</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>3.972986610441332</v>
+        <v>4.021532530207104</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>3.138285168378303</v>
+        <v>3.162242577327916</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>1.544140846847988</v>
+        <v>1.592152525838308</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>3.341223146457388</v>
+        <v>3.390470708851105</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>2.902882499368658</v>
+        <v>2.976139609148355</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>3.562397665302861</v>
+        <v>3.661744990597434</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>2.602979525910598</v>
+        <v>2.702887561929273</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.3732067348696901</v>
+        <v>0.4969033558979348</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-1.55637808070778</v>
+        <v>-1.407688532929953</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.1985669587831325</v>
+        <v>-0.02656819921647013</v>
       </c>
     </row>
     <row r="15">
@@ -1043,46 +1043,46 @@
         <v>213</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-1.77669067842168</v>
+        <v>-1.805886472774311</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.3679917731154347</v>
+        <v>0.366804986670779</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-3.313164588165478</v>
+        <v>-3.313317978169799</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-5.99984085302782</v>
+        <v>-6.000335345405823</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-7.007613974198584</v>
+        <v>-6.959068054432812</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-9.057657784939082</v>
+        <v>-9.033700375989469</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-9.1423681442052</v>
+        <v>-9.094356465214879</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-8.670469651841699</v>
+        <v>-8.621222089447983</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-9.670418944514765</v>
+        <v>-9.597161834735068</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-10.98982130891964</v>
+        <v>-10.89047398362506</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-8.847104626804345</v>
+        <v>-8.74719659078567</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-13.97704572327532</v>
+        <v>-13.85334910224707</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-16.27513084888913</v>
+        <v>-16.12644130111131</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-17.45784590288796</v>
+        <v>-17.2858471433213</v>
       </c>
     </row>
     <row r="16">
@@ -1095,46 +1095,46 @@
         <v>219</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.8827425145526178</v>
+        <v>-0.9119383089052491</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>3.8987654563105</v>
+        <v>3.897578669865844</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>3.503994071555461</v>
+        <v>3.503840681551139</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>4.54746122427624</v>
+        <v>4.546966731898237</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>2.639308657481912</v>
+        <v>2.687854577247684</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>2.023440677984574</v>
+        <v>2.047398086934187</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.3443747041126883</v>
+        <v>-0.2963630251223677</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>2.384903684064042</v>
+        <v>2.434151246457759</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>3.237163536673734</v>
+        <v>3.31042064645343</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>5.126970767741135</v>
+        <v>5.226318093035708</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>4.46564860491474</v>
+        <v>4.565556640933416</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>7.696373789233526</v>
+        <v>7.820070410261771</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>7.732843940486276</v>
+        <v>7.881533488264104</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>3.392369545050705</v>
+        <v>3.564368304617368</v>
       </c>
     </row>
     <row r="17">
@@ -1147,46 +1147,46 @@
         <v>242</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>1.238092233928455</v>
+        <v>1.208896439575824</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.4533524218563159</v>
+        <v>0.4521656354116601</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1.711473599084798</v>
+        <v>1.711320209080476</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-3.943425224268992</v>
+        <v>-3.943919716646995</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-2.828822215381209</v>
+        <v>-2.780276295615437</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-2.944671326242002</v>
+        <v>-2.920713917292389</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-2.61615854501229</v>
+        <v>-2.568146866021969</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-1.843557767311431</v>
+        <v>-1.794310204917714</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-1.904539923834207</v>
+        <v>-1.831282814054511</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-1.928012439172335</v>
+        <v>-1.828665113877761</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-3.372383018920125</v>
+        <v>-3.27247498290145</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-2.098335445077204</v>
+        <v>-1.974638824048959</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-2.931709438886479</v>
+        <v>-2.783019891108651</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-3.119196929155812</v>
+        <v>-2.94719816958915</v>
       </c>
     </row>
     <row r="18">
@@ -1199,46 +1199,46 @@
         <v>175</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-1.052344601962929</v>
+        <v>-1.08154039631556</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-8.377816409312466</v>
+        <v>-8.379003195757122</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-11.05830207978179</v>
+        <v>-11.05845546978611</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-12.07093407905051</v>
+        <v>-12.07142857142851</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-12.60922363214627</v>
+        <v>-12.5606777123805</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-14.02613531679683</v>
+        <v>-14.00217790784722</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-16.96798853320585</v>
+        <v>-16.91997685421553</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-15.72077146270694</v>
+        <v>-15.67152390031323</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-18.067467904944</v>
+        <v>-17.99421079516431</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-14.91738670127387</v>
+        <v>-14.8180393759793</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-13.97923071667698</v>
+        <v>-13.8793226806583</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-13.37342399289309</v>
+        <v>-13.24972737186484</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-9.222146274777856</v>
+        <v>-9.073456727000028</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-9.567839195979893</v>
+        <v>-9.395840436413231</v>
       </c>
     </row>
     <row r="19">
@@ -1251,46 +1251,46 @@
         <v>90</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>5.296861747243419</v>
+        <v>5.267665952890788</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>8.130120098624161</v>
+        <v>8.128933312179505</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>4.402015380535673</v>
+        <v>4.401861990531351</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>7.865573857457363</v>
+        <v>7.86507936507936</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>7.327284304361548</v>
+        <v>7.37583022412732</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>7.624658333996635</v>
+        <v>7.648615742946248</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>7.539947974730588</v>
+        <v>7.587959653720908</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>11.51732377538828</v>
+        <v>11.566571337782</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>12.56745272997675</v>
+        <v>12.64070983975645</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>9.495311711424421</v>
+        <v>9.594659036718994</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>8.17949944205337</v>
+        <v>8.279407478072045</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>9.324988705519679</v>
+        <v>9.448685326547924</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>5.571504518873056</v>
+        <v>5.720194066650883</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>2.463906835766139</v>
+        <v>2.635905595332801</v>
       </c>
     </row>
     <row r="20">
@@ -1303,98 +1303,98 @@
         <v>115</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1.432127447726515</v>
+        <v>1.402931653373884</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-2.787754297511277</v>
+        <v>-2.788941083955933</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.5738300300923527</v>
+        <v>-0.573983420096674</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-2.1827353212867</v>
+        <v>-2.183229813664703</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.7572359951830236</v>
+        <v>0.8057819149487955</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-2.423650844747151</v>
+        <v>-2.399693435797538</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.9698996655517433</v>
+        <v>1.017911344542064</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1.372396239156409</v>
+        <v>1.421643801550125</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-3.03641200432299</v>
+        <v>-2.963154894543294</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-4.755896018043906</v>
+        <v>-4.656548692749332</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-10.17798848065202</v>
+        <v>-10.07808044463334</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-10.14361032829665</v>
+        <v>-10.0199137072684</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-8.824630746827644</v>
+        <v>-8.675941199049817</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-10.33802553138362</v>
+        <v>-10.16602677181696</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 69.4</t>
+          <t>X ≈ 69.39</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>169</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-2.185058042368674</v>
+        <v>-2.214253836721305</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-2.021096206438415</v>
+        <v>-2.022282992883071</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>3.501292172120152</v>
+        <v>3.501138782115831</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>7.181813173696682</v>
+        <v>7.181318681318679</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>4.276659715275542</v>
+        <v>4.325205635041314</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>6.349181673904681</v>
+        <v>6.373139082854294</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>4.489323385644461</v>
+        <v>4.537335064634782</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>4.022254741857694</v>
+        <v>4.07150230425141</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.4109767273468066</v>
+        <v>0.4842338371265029</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-2.805805974308562</v>
+        <v>-2.706458649013989</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>2.314936654413501</v>
+        <v>2.414844690432176</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>2.941030783100217</v>
+        <v>3.064727404128462</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>6.662891764106334</v>
+        <v>6.811581311884161</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>5.705195461670144</v>
+        <v>5.877194221236806</v>
       </c>
     </row>
     <row r="22">
@@ -1407,46 +1407,46 @@
         <v>121</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-2.067692890038487</v>
+        <v>-2.096888684391118</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-6.158217826077475</v>
+        <v>-6.159404612522131</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-7.379435491824339</v>
+        <v>-7.37958888182866</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-4.769871505260724</v>
+        <v>-4.770365997638727</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-3.655268496372955</v>
+        <v>-3.606722576607183</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-3.357894466737868</v>
+        <v>-3.333937057788255</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-2.616158545012347</v>
+        <v>-2.568146866022026</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-3.909673469790718</v>
+        <v>-3.860425907397001</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>2.64091462162029</v>
+        <v>2.714171731399986</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.9645495442987411</v>
+        <v>1.063896869593314</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.7598483860385485</v>
+        <v>0.8597564220572238</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.858666023589592</v>
+        <v>-0.7349694025613474</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>1.200521966072152</v>
+        <v>1.34921151384998</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>3.905596459273895</v>
+        <v>4.077595218840557</v>
       </c>
     </row>
     <row r="23">
@@ -1459,46 +1459,46 @@
         <v>65</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-1.711685261303586</v>
+        <v>-1.740881055656217</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-4.86133289282904</v>
+        <v>-4.862519679273696</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-6.794565816045441</v>
+        <v>-6.794719206049763</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-6.664340672457165</v>
+        <v>-6.664835164835168</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-8.741091764014399</v>
+        <v>-8.692545844248627</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-8.443717734379312</v>
+        <v>-8.419760325429699</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-5.451505016722315</v>
+        <v>-5.403493337731994</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-1.303189045124526</v>
+        <v>-1.253941482730809</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.1742903368142379</v>
+        <v>0.2475474465939342</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>2.401294617407459</v>
+        <v>2.500641942702032</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>2.196593459147174</v>
+        <v>2.296501495165849</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-3.922874542343479</v>
+        <v>-3.799177921315234</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-4.343025395656888</v>
+        <v>-4.19433584787906</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-1.040366668507275</v>
+        <v>-0.8683679089406127</v>
       </c>
     </row>
     <row r="24">
@@ -1511,46 +1511,46 @@
         <v>96</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-2.480916030534353</v>
+        <v>-2.510111824886984</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>2.157897876401854</v>
+        <v>2.156711089957199</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>2.804793158313444</v>
+        <v>2.804639768309123</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>5.018351635235177</v>
+        <v>5.017857142857174</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>7.605062082139447</v>
+        <v>7.653608001905219</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>6.860769445107891</v>
+        <v>6.884726854057504</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>2.60939241917503</v>
+        <v>2.657404098165351</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-2.024342891278373</v>
+        <v>-1.975095328884656</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>5.206341618865551</v>
+        <v>5.279598728645247</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>5.398089489202349</v>
+        <v>5.497436814496922</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>8.318388330942199</v>
+        <v>8.418296366960874</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>4.18609981663073</v>
+        <v>4.309796437658974</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>7.93261562998407</v>
+        <v>8.081305177761898</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>5.033351280210603</v>
+        <v>5.205350039777265</v>
       </c>
     </row>
     <row r="25">
@@ -1563,46 +1563,46 @@
         <v>67</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>11.69818844707753</v>
+        <v>11.6689926527249</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>8.594465040580971</v>
+        <v>8.593278254136315</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>11.18476828269156</v>
+        <v>11.18461489268724</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>14.30006805314554</v>
+        <v>14.29957356076754</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>15.25431581348268</v>
+        <v>15.30286173324846</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>17.04422715655062</v>
+        <v>17.06818456550023</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>15.46697948385166</v>
+        <v>15.51499116284198</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>12.0148362131992</v>
+        <v>12.06408377559291</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>10.46131674324359</v>
+        <v>10.53457385302328</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>15.58154720064508</v>
+        <v>15.68089452593965</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>15.37684604238491</v>
+        <v>15.47675407840359</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>16.90376150817308</v>
+        <v>17.02745812920133</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>10.51346140112828</v>
+        <v>10.66215094890611</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>16.70934630508611</v>
+        <v>16.88134506465277</v>
       </c>
     </row>
     <row r="26">
@@ -1615,46 +1615,46 @@
         <v>38</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>8.045399758939332</v>
+        <v>8.016203964586701</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>11.69737156061235</v>
+        <v>11.6961847741677</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>8.671021228488883</v>
+        <v>8.670867838484561</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>11.43282531944573</v>
+        <v>11.43233082706773</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>16.15769366108697</v>
+        <v>16.20623958085275</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>19.08664663809031</v>
+        <v>19.11060404703993</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>16.37035733145574</v>
+        <v>16.41836901044606</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>18.53486763503756</v>
+        <v>18.58411519743128</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>23.73704337325148</v>
+        <v>23.81030048303118</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>25.51870352429012</v>
+        <v>25.61805084958469</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>20.05084447129302</v>
+        <v>20.15075250731169</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>14.82206472891141</v>
+        <v>14.94576134993965</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>17.03349282296658</v>
+        <v>17.18218237074441</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>9.364491631087837</v>
+        <v>9.5364903906545</v>
       </c>
     </row>
     <row r="27">
@@ -1667,46 +1667,46 @@
         <v>29</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-7.653329823637698</v>
+        <v>-7.682525617990329</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-5.816240054632665</v>
+        <v>-5.817426841077321</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-6.211011439387704</v>
+        <v>-6.211164829392025</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-6.080786295799342</v>
+        <v>-6.081280788177345</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>7.174027599380729</v>
+        <v>7.222573519146501</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>4.023125766947047</v>
+        <v>4.04708317589666</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>7.386691269749647</v>
+        <v>7.434702948739968</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>0.02307090182497262</v>
+        <v>0.07231846421868937</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-6.934462978835732</v>
+        <v>-6.861205869056036</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-7.784381775165592</v>
+        <v>-7.685034449871019</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-1.092531209287756</v>
+        <v>-0.9926231732690809</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-11.40298064313922</v>
+        <v>-11.27928402211098</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-15.2714073585217</v>
+        <v>-15.12271781074387</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-15.04567170829517</v>
+        <v>-14.8736729487285</v>
       </c>
     </row>
     <row r="28">
@@ -1719,46 +1719,46 @@
         <v>22</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-2.480916030534289</v>
+        <v>-2.51011182488692</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.4533524218563016</v>
+        <v>0.4521656354116459</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>13.69494467346495</v>
+        <v>13.69479128346063</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>18.37062436250773</v>
+        <v>18.37012987012973</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>22.37778935486671</v>
+        <v>22.42633527463249</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.05210934277104684</v>
+        <v>-0.02815193382143377</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>8.954089388872134</v>
+        <v>9.002101067862455</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>3.941566199630657</v>
+        <v>3.990813762024374</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>3.880584043108009</v>
+        <v>3.953841152887705</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>12.12157433768711</v>
+        <v>12.22092166298168</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>16.46232772488153</v>
+        <v>16.56223576090021</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>11.95125133178244</v>
+        <v>12.07494795281068</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-2.105263157894868</v>
+        <v>-1.95657361011704</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-15.51589114403198</v>
+        <v>-15.34389238446531</v>
       </c>
     </row>
     <row r="29">
@@ -1771,46 +1771,46 @@
         <v>27</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.6290641786825475</v>
+        <v>-0.6582599730351788</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-2.24025027174622</v>
+        <v>-2.241437058190876</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>1.06868204720228</v>
+        <v>1.068528657197959</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-6.208500216616656</v>
+        <v>-6.208994708994659</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-10.45049347341611</v>
+        <v>-10.40194755365034</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-6.44941574007732</v>
+        <v>-6.425458331127707</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0.8732813080639232</v>
+        <v>0.9212929870542439</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-7.001194743130121</v>
+        <v>-6.951947180736404</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0.3452305077544082</v>
+        <v>0.4184876175341046</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-4.208391992279047</v>
+        <v>-4.109044666984474</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>10.40172166427546</v>
+        <v>10.50162970029413</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>14.13980352033439</v>
+        <v>14.26350014136263</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>17.42335637072473</v>
+        <v>17.57204591850256</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>17.64909202095148</v>
+        <v>17.82109078051814</v>
       </c>
     </row>
     <row r="30">
@@ -1823,46 +1823,46 @@
         <v>25</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>3.519083969465655</v>
+        <v>3.489888175113023</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-2.092102123598238</v>
+        <v>-2.093288910042894</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-6.48687350835322</v>
+        <v>-6.487026898357541</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>1.643351635235028</v>
+        <v>1.642857142857025</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>13.10506208213945</v>
+        <v>13.15360800190522</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>17.40243611177448</v>
+        <v>17.42639352072409</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>17.31772575250831</v>
+        <v>17.36573743149863</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>16.85065710872157</v>
+        <v>16.89990467111529</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>16.78967495219891</v>
+        <v>16.8629320619786</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>15.93975615586893</v>
+        <v>16.03910348116351</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>7.735054997608799</v>
+        <v>7.834963033627474</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>11.76943314996412</v>
+        <v>11.89312977099237</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>11.34928229665077</v>
+        <v>11.4979718444286</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>11.57501794687719</v>
+        <v>11.74701670644385</v>
       </c>
     </row>
     <row r="31">
@@ -1875,46 +1875,46 @@
         <v>21</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-4.861868411486739</v>
+        <v>-4.891064205839371</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>12.57456454306848</v>
+        <v>12.57337775662382</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>12.17979315831351</v>
+        <v>12.17963976830919</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>12.31001830190187</v>
+        <v>12.30952380952387</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>16.53363351071088</v>
+        <v>16.58217943047665</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>16.83100754034604</v>
+        <v>16.85496494929565</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>11.98439241917509</v>
+        <v>12.03240409816542</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>1.993514251578766</v>
+        <v>2.042761813972483</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>11.45634161886551</v>
+        <v>11.5295987286452</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>10.60642282253565</v>
+        <v>10.70577014783022</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>10.40172166427546</v>
+        <v>10.50162970029413</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>5.674195054726027</v>
+        <v>5.797891675754272</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>5.254044201412619</v>
+        <v>5.402733749190446</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>5.479779851639151</v>
+        <v>5.651778611205813</v>
       </c>
     </row>
     <row r="32">
@@ -1927,46 +1927,46 @@
         <v>25</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.4809160305343525</v>
+        <v>-0.5101118248869838</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-14.09210212359824</v>
+        <v>-14.09328891004289</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-10.48687350835322</v>
+        <v>-10.48702689835754</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-6.356648364764858</v>
+        <v>-6.357142857142861</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-10.89493791786055</v>
+        <v>-10.84639199809478</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>1.402436111774541</v>
+        <v>1.426393520724154</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>5.317725752508366</v>
+        <v>5.365737431498687</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>4.850657108721606</v>
+        <v>4.899904671115323</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0.7896749521988582</v>
+        <v>0.8629320619785545</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>3.939756155868992</v>
+        <v>4.039103481163565</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>3.735054997608742</v>
+        <v>3.834963033627417</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>3.769433149964122</v>
+        <v>3.893129770992367</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>3.349282296650713</v>
+        <v>3.497971844428541</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>3.575017946877246</v>
+        <v>3.747016706443908</v>
       </c>
     </row>
     <row r="33">
@@ -1979,46 +1979,46 @@
         <v>17</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.4602604400538866</v>
+        <v>0.4310646457012552</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-1.150925653009864</v>
+        <v>-1.15211243945452</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-13.31040292011793</v>
+        <v>-13.31055631012225</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-19.06253071770603</v>
+        <v>-19.06302521008404</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-25.4831732119782</v>
+        <v>-25.43462729221243</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-25.18579918234311</v>
+        <v>-25.1618417733935</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-19.38815660043281</v>
+        <v>-19.34014492144249</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-13.97287230304303</v>
+        <v>-13.92362474064932</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-14.03385445956586</v>
+        <v>-13.96059734978616</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-14.88377325589572</v>
+        <v>-14.78442593060115</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-9.206121472979355</v>
+        <v>-9.10621343696068</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-9.171743320624117</v>
+        <v>-9.048046699595872</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-9.591894173937526</v>
+        <v>-9.443204626159698</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-9.366158523711029</v>
+        <v>-9.194159764144366</v>
       </c>
     </row>
     <row r="34">
@@ -2031,46 +2031,46 @@
         <v>18</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-8.03647158608991</v>
+        <v>-8.065667380442541</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-15.20321323470929</v>
+        <v>-15.20440002115394</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-21.15354017501993</v>
+        <v>-21.15369356502425</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-21.02331503143157</v>
+        <v>-21.02380952380957</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-27.11716014008277</v>
+        <v>-27.068614220317</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-21.26423055489214</v>
+        <v>-21.24027314594252</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-32.46005202526941</v>
+        <v>-32.41204034627909</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-27.37156511350059</v>
+        <v>-27.32231755110688</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-27.43254727002337</v>
+        <v>-27.35929016024367</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-28.28246606635323</v>
+        <v>-28.18311874105866</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-34.04272278016898</v>
+        <v>-33.9428147441503</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-45.11945573892477</v>
+        <v>-44.99575911789653</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-51.09516214779373</v>
+        <v>-50.9464726000159</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-50.86942649756716</v>
+        <v>-50.6974277380005</v>
       </c>
     </row>
   </sheetData>
@@ -2214,49 +2214,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4065</v>
+        <v>4076</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.151342710279323</v>
+        <v>-0.1501216072298561</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.1308561093720328</v>
+        <v>-0.1304709061289415</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.2670501521216195</v>
+        <v>-0.2663271185679719</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.246218916912099</v>
+        <v>-0.2455422697713487</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.2312167592940355</v>
+        <v>-0.2319489136394566</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.2395967878080825</v>
+        <v>-0.2396201913228708</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.1881681571183478</v>
+        <v>-0.1890017308819125</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.2733910366971912</v>
+        <v>-0.2740296747935318</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.1734700109461116</v>
+        <v>-0.175048825058937</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.2725810277142031</v>
+        <v>-0.2746220090325124</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.266911570729448</v>
+        <v>-0.2689840122170963</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.2925289842871663</v>
+        <v>-0.2951978405819276</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.3300093905111083</v>
+        <v>-0.3332766225815149</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.3610214135163616</v>
+        <v>-0.3648576802096741</v>
       </c>
     </row>
     <row r="7">
@@ -2266,49 +2266,49 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3928</v>
+        <v>3939</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.2860416331732765</v>
+        <v>-0.2833911771136997</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.4372797885728019</v>
+        <v>-0.4359869611691352</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.7676554326994989</v>
+        <v>-0.7655079110157672</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.6237890453133588</v>
+        <v>-0.6220200412401056</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.6404294088435307</v>
+        <v>-0.6417314104554706</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.5325232378189639</v>
+        <v>-0.532562648518315</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.6797329514306441</v>
+        <v>-0.6808920667273668</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.7772025760775634</v>
+        <v>-0.7781688396577877</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.6718048342237282</v>
+        <v>-0.6745932929910268</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.7194503548125937</v>
+        <v>-0.7237674293106977</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.6556852720426889</v>
+        <v>-0.6602170779909997</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.6071571808246787</v>
+        <v>-0.6133406679825129</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.6313743589868466</v>
+        <v>-0.6390839931349106</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.6714178983366068</v>
+        <v>-0.6805029686005142</v>
       </c>
     </row>
     <row r="8">
@@ -2318,153 +2318,153 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3723</v>
+        <v>3734</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.4734213838534131</v>
+        <v>-0.4684785182416675</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.4642574114161206</v>
+        <v>-0.4627496681848626</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.7375430316526348</v>
+        <v>-0.735358006501734</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.5929194603983987</v>
+        <v>-0.591117216117226</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.6344877570888556</v>
+        <v>-0.6385373360589739</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.5637927812836239</v>
+        <v>-0.5650549025789005</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.7144458292610665</v>
+        <v>-0.7181973452989681</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.6843388687522278</v>
+        <v>-0.6883306230023081</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.5965911422217545</v>
+        <v>-0.6037702648468084</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.6805819176485812</v>
+        <v>-0.6906985520092519</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.5751972836579711</v>
+        <v>-0.5856952484169469</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.6064057762103729</v>
+        <v>-0.6197181947463903</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.689385802167763</v>
+        <v>-0.7055087445942192</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.7977996733215207</v>
+        <v>-0.8164541023402379</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; 28.04</t>
+          <t>X &gt; 28.05</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3523</v>
+        <v>3534</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.670961279403123</v>
+        <v>-0.663480869149744</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.5418899595246316</v>
+        <v>-0.539989417657047</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.6951361003170007</v>
+        <v>-0.6929507347468231</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.5213808867008964</v>
+        <v>-0.5196710738471495</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.5348020175208106</v>
+        <v>-0.5421300731724017</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.5052387678629628</v>
+        <v>-0.5081067616022281</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.6029541341771889</v>
+        <v>-0.6099756439037378</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.4596290913350458</v>
+        <v>-0.4673269673027391</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.4484202858963826</v>
+        <v>-0.460605660541944</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.4322313689396253</v>
+        <v>-0.4493080507753859</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.3375485191240486</v>
+        <v>-0.3550284846083187</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.2305668500358706</v>
+        <v>-0.2527978308175847</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.3226813809883353</v>
+        <v>-0.3492700226153076</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.5351154621491503</v>
+        <v>-0.5653771815017592</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; 31.35</t>
+          <t>X &gt; 31.36</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3284</v>
+        <v>3295</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.8885593426362632</v>
+        <v>-0.877705537099807</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.8154030944719608</v>
+        <v>-0.8123696478716838</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.8905153899920677</v>
+        <v>-0.8875108668995892</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.956526931856537</v>
+        <v>-0.9532094229522414</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.8408838638064964</v>
+        <v>-0.8512346131068895</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.8004800486142827</v>
+        <v>-0.8043058434902122</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-1.203088589636877</v>
+        <v>-1.212094185703009</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-1.197975110123359</v>
+        <v>-1.207335559117915</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-1.181744932264507</v>
+        <v>-1.197673998627508</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-1.133236544860935</v>
+        <v>-1.156410310894628</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.9561527906479697</v>
+        <v>-0.9800763842015101</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.9962394002488963</v>
+        <v>-1.02649412952325</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-1.186486348706971</v>
+        <v>-1.222901941979224</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-1.370170847276221</v>
+        <v>-1.412315615255636</v>
       </c>
     </row>
     <row r="11">
@@ -2474,49 +2474,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3045</v>
+        <v>3055</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.7962578689380209</v>
+        <v>-0.8298508134677363</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.5907932230746198</v>
+        <v>-0.6185743912826425</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.6407196621993734</v>
+        <v>-0.6534216781291562</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.9185344158454072</v>
+        <v>-0.9150547657888595</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.8497364766551811</v>
+        <v>-0.864668760496869</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.8295429183696328</v>
+        <v>-0.8354412817570775</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-1.42104841989412</v>
+        <v>-1.433740034209997</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-1.34606420275378</v>
+        <v>-1.359487684324058</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-1.454995431533519</v>
+        <v>-1.476937219067203</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-1.401451193212381</v>
+        <v>-1.433273112494497</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-1.194383794645873</v>
+        <v>-1.22716907886435</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-1.389739807042766</v>
+        <v>-1.412725642812021</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-1.49641698109059</v>
+        <v>-1.528206166042665</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-1.613816207474152</v>
+        <v>-1.621232066060188</v>
       </c>
     </row>
     <row r="12">
@@ -2529,46 +2529,46 @@
         <v>2762</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.6344279783982216</v>
+        <v>-0.6636237727508529</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.6525655558936236</v>
+        <v>-0.6537523423382794</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.8663087002431595</v>
+        <v>-0.8664620902474809</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-1.2791682778713</v>
+        <v>-1.279662770249303</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-1.020933573182781</v>
+        <v>-0.9723876534170088</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-1.302849912845303</v>
+        <v>-1.27889250389569</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-1.496177216354774</v>
+        <v>-1.448165537364453</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-1.456366787006104</v>
+        <v>-1.407119224612387</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-1.481143295447779</v>
+        <v>-1.407886185668083</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-1.679360426317835</v>
+        <v>-1.580013101023262</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-1.413388159523713</v>
+        <v>-1.313480123505038</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-1.777272136060503</v>
+        <v>-1.653575515032259</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-1.871572156644</v>
+        <v>-1.722882608866172</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-2.261332523796177</v>
+        <v>-2.089333764229515</v>
       </c>
     </row>
     <row r="13">
@@ -2581,46 +2581,46 @@
         <v>2419</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.02011745437676637</v>
+        <v>-0.009078339975864935</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.06151097022902263</v>
+        <v>-0.06269775667367838</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.04288839053593563</v>
+        <v>-0.04304178054025698</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.1606996256164521</v>
+        <v>-0.1611941179944552</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.120237628484773</v>
+        <v>-0.07169170871900121</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.3602757526322478</v>
+        <v>-0.3363183436826347</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.5690043012328516</v>
+        <v>-0.520992622242531</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.4159819983474122</v>
+        <v>-0.3667344359536955</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.3116065690909409</v>
+        <v>-0.2383494593112445</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.2107192471901271</v>
+        <v>-0.1113719218955538</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.1219917483322348</v>
+        <v>0.2218997843509101</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.4637210459846202</v>
+        <v>-0.3400244249563755</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.5944961241843458</v>
+        <v>-0.4458065764065182</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-1.236887799298863</v>
+        <v>-1.064889039732201</v>
       </c>
     </row>
     <row r="14">
@@ -2633,46 +2633,46 @@
         <v>2143</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.06224775854637699</v>
+        <v>0.03305196419374568</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.1490316616289817</v>
+        <v>-0.1502184480736375</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.03050393299157861</v>
+        <v>-0.03065732299589996</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.09972121059678329</v>
+        <v>0.09922671821878026</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.1680578824194257</v>
+        <v>0.2166038021851975</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.09453075710087688</v>
+        <v>-0.07057334815126381</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.6458766739965327</v>
+        <v>-0.597864995006212</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.4129919813390401</v>
+        <v>-0.3637444189453234</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.1939928032841181</v>
+        <v>-0.1207356935044217</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-0.1106404843549953</v>
+        <v>-0.01129315906042194</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.3379481380660962</v>
+        <v>0.4378561740847715</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.4209541575487137</v>
+        <v>-0.297257536520469</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.7477778993362207</v>
+        <v>-0.5990883515583931</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-1.361986252842776</v>
+        <v>-1.189987493276114</v>
       </c>
     </row>
     <row r="15">
@@ -2685,46 +2685,46 @@
         <v>1878</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.0217463762814063</v>
+        <v>-0.007449418071225011</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.04524376364077654</v>
+        <v>-0.04643055008543229</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.1737744668196797</v>
+        <v>-0.173927856824001</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.2565418684922349</v>
+        <v>-0.257036360870238</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.3688463310660879</v>
+        <v>-0.3203004113003161</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.5507055282680611</v>
+        <v>-0.526748119318448</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.954904705425605</v>
+        <v>-0.9068930264352844</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.9427401223752838</v>
+        <v>-0.8934925599815671</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.6309853246914585</v>
+        <v>-0.5577282149117622</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.6289339399776495</v>
+        <v>-0.5295866146830761</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.01833508280581952</v>
+        <v>0.1182431188244948</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.5330162643063758</v>
+        <v>-0.4093196432781312</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.6336782997284161</v>
+        <v>-0.4849887519505884</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-1.526153512121688</v>
+        <v>-1.354154752555026</v>
       </c>
     </row>
     <row r="16">
@@ -2737,46 +2737,46 @@
         <v>1665</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.2518167021983828</v>
+        <v>0.2226209078457515</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.09810812960418502</v>
+        <v>-0.09929491604884078</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.2278412063614965</v>
+        <v>0.2276878163571752</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.4781864700699785</v>
+        <v>0.4776919776919755</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.4804374575148245</v>
+        <v>0.5289833772805963</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.5375712469096712</v>
+        <v>0.5615286558592842</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.09250052728313563</v>
+        <v>0.1405122062734563</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.04585230391681705</v>
+        <v>0.0950998663105338</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.5254106879345883</v>
+        <v>0.5986677977142847</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.6965129126257494</v>
+        <v>0.7958602379203228</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>1.152472415026217</v>
+        <v>1.252380451044893</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>1.186850567381541</v>
+        <v>1.310547188409785</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>1.367300314668725</v>
+        <v>1.515989862446553</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.5119548838141768</v>
+        <v>0.6839536433808391</v>
       </c>
     </row>
     <row r="17">
@@ -2789,46 +2789,46 @@
         <v>1446</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.4236482848183485</v>
+        <v>0.3944524904657172</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.703443755686699</v>
+        <v>-0.7046305421313548</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.2683396217695417</v>
+        <v>-0.2684930117738631</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.1381144781811798</v>
+        <v>-0.1386089705591829</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.1534714873953291</v>
+        <v>0.2020174071611009</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.3125329305850499</v>
+        <v>0.336490339534663</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.1586662780961987</v>
+        <v>0.2066779570865194</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.3084023656905401</v>
+        <v>-0.2591548032968234</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.1147095303454648</v>
+        <v>0.1879666401251612</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.02550995946511847</v>
+        <v>0.1248572847596918</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.6506843198771222</v>
+        <v>0.7505923558957974</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.2009684196736643</v>
+        <v>0.3246650407019089</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.4032242053644026</v>
+        <v>0.5519137531422302</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.07570950980947089</v>
+        <v>0.2477082693761332</v>
       </c>
     </row>
     <row r="18">
@@ -2841,46 +2841,46 @@
         <v>1204</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.2599477568410649</v>
+        <v>0.2307519624884335</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.9359559441961807</v>
+        <v>-0.9371427306408364</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.6662755017087036</v>
+        <v>-0.666428891713025</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.6267403395540754</v>
+        <v>0.6262458471760723</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.7529026137009112</v>
+        <v>0.801448533466683</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.96722016493068</v>
+        <v>0.991177573880293</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.7163968488538828</v>
+        <v>0.7644085278442034</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.0001587698511897884</v>
+        <v>0.04940633224490654</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.5205719621656257</v>
+        <v>0.5938290719453221</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.4181614714836144</v>
+        <v>0.5175087967781877</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>1.45930748930315</v>
+        <v>1.559215525321825</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.663120857605314</v>
+        <v>0.7868174786335587</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1.073534788345064</v>
+        <v>1.222224336122892</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.7178750897343846</v>
+        <v>0.889873849301047</v>
       </c>
     </row>
     <row r="19">
@@ -2893,46 +2893,46 @@
         <v>1029</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.4831267294267718</v>
+        <v>0.4539309350741405</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.3296665838848156</v>
+        <v>0.3284797974401599</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1.101075957147266</v>
+        <v>1.100922567142945</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>2.786208778092281</v>
+        <v>2.785714285714278</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>3.02537306367492</v>
+        <v>3.073918983440691</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>3.517110552979581</v>
+        <v>3.541067961929194</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>3.723945383217789</v>
+        <v>3.771957062208109</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>2.673786360422305</v>
+        <v>2.723033922816022</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>3.681803232082231</v>
+        <v>3.755060341861927</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>3.026247895421953</v>
+        <v>3.125595220716527</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>4.084909225014052</v>
+        <v>4.184817261032727</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>3.050288349186673</v>
+        <v>3.173984970214917</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>2.824500955542838</v>
+        <v>2.973190503320666</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>2.467146226760626</v>
+        <v>2.639144986327288</v>
       </c>
     </row>
     <row r="20">
@@ -2945,98 +2945,98 @@
         <v>939</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.0217463762814063</v>
+        <v>-0.007449418071225011</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.4179807178473851</v>
+        <v>-0.4191675042920409</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.7846919868544475</v>
+        <v>0.7845385968501262</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>2.299368674638757</v>
+        <v>2.298874182260754</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>2.613049302586738</v>
+        <v>2.66159522235251</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>3.123415877482735</v>
+        <v>3.147373286432348</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>3.358194336107935</v>
+        <v>3.406206015098256</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1.826162966016625</v>
+        <v>1.875410528410342</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>2.83014353579842</v>
+        <v>2.903400645578117</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>2.406209829990402</v>
+        <v>2.505557155284976</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>3.692456488556616</v>
+        <v>3.792364524575291</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>2.44887936934645</v>
+        <v>2.572575990374695</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>2.56120987918532</v>
+        <v>2.709899426963148</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>2.467456711520484</v>
+        <v>2.639455471087146</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 67.75</t>
+          <t>X &gt; 67.74</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>824</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.175090787815904</v>
+        <v>-0.2042865821685353</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.08724775466613721</v>
+        <v>-0.08843454111079296</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.974291540190471</v>
+        <v>0.9741381501861497</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>2.924905033293392</v>
+        <v>2.924410540915389</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>2.87205237340158</v>
+        <v>2.920598293167352</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>3.89758174284249</v>
+        <v>3.921539151792103</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>3.691512160275359</v>
+        <v>3.739523839265679</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.889492060177936</v>
+        <v>1.938739622571653</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>3.648898253169726</v>
+        <v>3.722155362949422</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>3.405775573344712</v>
+        <v>3.505122898639286</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>5.628258881103939</v>
+        <v>5.728166917122614</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>4.206326353847615</v>
+        <v>4.33002297487586</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>4.150253170437125</v>
+        <v>4.298942718214953</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>4.25462959736268</v>
+        <v>4.426628356929342</v>
       </c>
     </row>
     <row r="22">
@@ -3049,46 +3049,46 @@
         <v>655</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.3435114503816763</v>
+        <v>0.314315656029045</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.4117146702949555</v>
+        <v>0.4105278838502997</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.3222867969902907</v>
+        <v>0.3221334069859694</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1.826557742105372</v>
+        <v>1.826063249727369</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>2.509642234811203</v>
+        <v>2.558188154576975</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>3.265031531621865</v>
+        <v>3.288988940571478</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>3.485664683806078</v>
+        <v>3.533676362796399</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>1.339206727042246</v>
+        <v>1.388454289435963</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>4.484331440748463</v>
+        <v>4.557588550528159</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>5.00845844594533</v>
+        <v>5.107805771239903</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>6.483146600662238</v>
+        <v>6.583054636680913</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>4.532791928590079</v>
+        <v>4.656488549618324</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>3.501954052375908</v>
+        <v>3.650643600153735</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>3.880361458327627</v>
+        <v>4.052360217894289</v>
       </c>
     </row>
     <row r="23">
@@ -3101,46 +3101,46 @@
         <v>534</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.8898704863195803</v>
+        <v>0.860674691966949</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>1.900407239697699</v>
+        <v>1.899220453253044</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>2.067433607751653</v>
+        <v>2.067280217747332</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>3.321254256957985</v>
+        <v>3.320759764579982</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>3.906560209480268</v>
+        <v>3.95510612924604</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>4.765731991924348</v>
+        <v>4.789689400873961</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>4.868287550261179</v>
+        <v>4.9162992292515</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>2.528559730444471</v>
+        <v>2.577807292838187</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>4.90203450276065</v>
+        <v>4.975291612540346</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>5.924774882460746</v>
+        <v>6.024122207755319</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>7.779998817833516</v>
+        <v>7.879906853852191</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>5.754451876555876</v>
+        <v>5.878148497584121</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>4.023439600021504</v>
+        <v>4.172129147799332</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>3.874643415042044</v>
+        <v>4.046642174608706</v>
       </c>
     </row>
     <row r="24">
@@ -3153,46 +3153,46 @@
         <v>469</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1.250427253047739</v>
+        <v>1.221231458695108</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>2.837535403054275</v>
+        <v>2.836348616609619</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>3.295642483117994</v>
+        <v>3.295489093113673</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>4.705185323934501</v>
+        <v>4.704690831556498</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>5.659433084271647</v>
+        <v>5.707979004037419</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>6.596465962520803</v>
+        <v>6.620423371470416</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>6.298535987049945</v>
+        <v>6.346547666040266</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>3.059612332602228</v>
+        <v>3.108859894995945</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>5.557265570535741</v>
+        <v>5.630522680315437</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>6.413103703843404</v>
+        <v>6.512451029137978</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>8.553818323834818</v>
+        <v>8.653726359853493</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>7.095659162757293</v>
+        <v>7.219355783785538</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>5.182970996011058</v>
+        <v>5.331660543788885</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>4.555828181418825</v>
+        <v>4.727826940985487</v>
       </c>
     </row>
     <row r="25">
@@ -3205,46 +3205,46 @@
         <v>373</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>2.210772977508547</v>
+        <v>2.181577183155916</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>3.012455517152496</v>
+        <v>3.01126873070784</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>3.421973676633378</v>
+        <v>3.421820286629057</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>4.624584879202963</v>
+        <v>4.62409038682496</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>5.158681385088506</v>
+        <v>5.207227304854278</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>6.528441473704824</v>
+        <v>6.552398882654437</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>7.248020658674584</v>
+        <v>7.296032337664904</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>4.368083382180068</v>
+        <v>4.417330944573784</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>5.647583799383831</v>
+        <v>5.720840909163527</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>6.67434060627113</v>
+        <v>6.773687931565703</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>8.614411565973413</v>
+        <v>8.714319601992088</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>7.844500174092808</v>
+        <v>7.968196795121052</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>4.475287658581003</v>
+        <v>4.62397720635883</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>4.432926794062226</v>
+        <v>4.604925553628888</v>
       </c>
     </row>
     <row r="26">
@@ -3257,98 +3257,98 @@
         <v>306</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0.1334630544329727</v>
+        <v>0.1042672600803414</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>1.79025081757829</v>
+        <v>1.789064031133634</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>1.722276818444165</v>
+        <v>1.722123428439843</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>2.506096733274354</v>
+        <v>2.505602240896351</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>2.948199337041416</v>
+        <v>2.996745256807188</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>4.225965523539244</v>
+        <v>4.249922932488857</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>5.448444706756732</v>
+        <v>5.496456385747052</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>2.693794363623596</v>
+        <v>2.743041926017312</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>4.593596520826303</v>
+        <v>4.666853630605999</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>4.724069881359185</v>
+        <v>4.823417206653758</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>7.13374780806631</v>
+        <v>7.233655844084986</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>5.860936417937978</v>
+        <v>5.984633038966223</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>3.153203865278165</v>
+        <v>3.301893413055993</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>1.744952587400128</v>
+        <v>1.91695134696679</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 87.6</t>
+          <t>X &gt; 87.59</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>268</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.9883787171015115</v>
+        <v>-1.017574511454143</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.3855098167003277</v>
+        <v>0.3843230302556719</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.7370070886617057</v>
+        <v>0.7368536986573844</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>1.240366560608273</v>
+        <v>1.23987206823027</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>1.075211335870783</v>
+        <v>1.123757255636555</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>2.118854022222294</v>
+        <v>2.142811431171907</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>3.899815304747172</v>
+        <v>3.947826983737492</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>0.447672034094758</v>
+        <v>0.4969195964884747</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>1.879227191004823</v>
+        <v>1.952484300784519</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>1.775577051391373</v>
+        <v>1.874924376685946</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>5.302219176713272</v>
+        <v>5.402127212731948</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>4.590328672352186</v>
+        <v>4.714025293380431</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>1.185103192173095</v>
+        <v>1.333792739950923</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>0.6645701856832176</v>
+        <v>0.8365689452498799</v>
       </c>
     </row>
     <row r="28">
@@ -3361,46 +3361,46 @@
         <v>239</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.1796608004088327</v>
+        <v>-0.208856594761464</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>1.138023399414372</v>
+        <v>1.136836612969716</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>1.58007209834134</v>
+        <v>1.579918708337019</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>2.128707283770702</v>
+        <v>2.128212791392698</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.3351876051520009</v>
+        <v>0.3837335249177727</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>1.887791760310094</v>
+        <v>1.911749169259707</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>3.476721568407953</v>
+        <v>3.524733247398274</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>0.4991926735751804</v>
+        <v>0.5484402359688971</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>2.948670768098438</v>
+        <v>3.021927877878134</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>2.935572055450585</v>
+        <v>3.034919380745158</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>6.078151231918426</v>
+        <v>6.178059267937101</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>6.530939426114749</v>
+        <v>6.654636047142994</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>3.181918279914306</v>
+        <v>3.330607827692134</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>2.570833846458839</v>
+        <v>2.742832606025502</v>
       </c>
     </row>
     <row r="29">
@@ -3413,46 +3413,46 @@
         <v>217</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.05364618144720623</v>
+        <v>0.02445038709457492</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>1.207437046908737</v>
+        <v>1.206250260464081</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.3518361690661322</v>
+        <v>0.3516827790618109</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.4820613126544941</v>
+        <v>0.4815668202764911</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-1.899546212791428</v>
+        <v>-1.851000293025656</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>2.084463761544121</v>
+        <v>2.108421170493735</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>2.921412388453064</v>
+        <v>2.969424067443384</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>0.1501962792285454</v>
+        <v>0.1994438416222621</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>2.854191081231114</v>
+        <v>2.927448191010811</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>2.004272284901255</v>
+        <v>2.103619610195828</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>5.025377578253959</v>
+        <v>5.125285614272634</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>5.981414716784393</v>
+        <v>6.105111337812637</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>3.717945891120763</v>
+        <v>3.866635438898591</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>4.404511034434854</v>
+        <v>4.576509794001517</v>
       </c>
     </row>
     <row r="30">
@@ -3465,46 +3465,46 @@
         <v>190</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.1506629168340652</v>
+        <v>0.1214671224814339</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>1.697371560612339</v>
+        <v>1.696184774167683</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.2499685969099446</v>
+        <v>0.2498152069056232</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>1.432825319445662</v>
+        <v>1.432330827067659</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.68441160207108</v>
+        <v>-0.6358656823053082</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>3.297172953879802</v>
+        <v>3.321130362829415</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>3.212462594613633</v>
+        <v>3.260474273603954</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>1.166446582405833</v>
+        <v>1.215694144799549</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>3.210727583777803</v>
+        <v>3.2839846935575</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>2.887124576921615</v>
+        <v>2.986471902216188</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>4.261370787082484</v>
+        <v>4.361278823101159</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>4.822064728911492</v>
+        <v>4.945761349939737</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>1.770334928229666</v>
+        <v>1.919024476007493</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>2.522386367929869</v>
+        <v>2.694385127496531</v>
       </c>
     </row>
     <row r="31">
@@ -3517,46 +3517,46 @@
         <v>165</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.3597039093222278</v>
+        <v>-0.3888997036748592</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>2.271534240038179</v>
+        <v>2.270347453593523</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>1.270702249222545</v>
+        <v>1.270548859218223</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>1.400927392810907</v>
+        <v>1.400432900432904</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-2.773725796648428</v>
+        <v>-2.725179876882656</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>1.160011869350299</v>
+        <v>1.183969278299912</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>1.075301510084131</v>
+        <v>1.123313189074452</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-1.209948951884428</v>
+        <v>-1.160701389490711</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>1.153311315835211</v>
+        <v>1.226568425614907</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>0.9094531255659604</v>
+        <v>1.008800450860534</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>3.735054997608799</v>
+        <v>3.834963033627474</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>3.769433149964122</v>
+        <v>3.893129770992367</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>0.3189792663476823</v>
+        <v>0.4676688141255099</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>1.150775522634824</v>
+        <v>1.322774282201486</v>
       </c>
     </row>
     <row r="32">
@@ -3569,46 +3569,46 @@
         <v>144</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.2968617472434261</v>
+        <v>0.2676659528907948</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.7690089875129331</v>
+        <v>0.7678222010682774</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.3202068416865558</v>
+        <v>-0.3203602316908771</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.1899816980981939</v>
+        <v>-0.1904761904761969</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-5.589382362304995</v>
+        <v>-5.540836442539224</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-1.125341666003244</v>
+        <v>-1.101384257053631</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.5156075808249696</v>
+        <v>-0.4675959018346489</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-1.677120669056151</v>
+        <v>-1.627873106662435</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.3492139366900346</v>
+        <v>-0.2759568269103383</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.5046882885754513</v>
+        <v>-0.405340963280878</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>2.762832775386578</v>
+        <v>2.862740811405253</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>3.491655372186344</v>
+        <v>3.615351993214588</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.4007177033492866</v>
+        <v>-0.252028155571459</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0.5194623913216887</v>
+        <v>0.691461150888351</v>
       </c>
     </row>
     <row r="33">
@@ -3621,98 +3621,98 @@
         <v>119</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.4602604400538866</v>
+        <v>0.4310646457012552</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>3.89109115371275</v>
+        <v>3.889904367268095</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>1.81564750005014</v>
+        <v>1.815494110045819</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>1.105536509184724</v>
+        <v>1.105042016806721</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-4.474769850633663</v>
+        <v>-4.426223930867891</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-1.656387417637227</v>
+        <v>-1.632430008687614</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-1.741097776903395</v>
+        <v>-1.693086097913074</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-3.048502555143912</v>
+        <v>-2.999254992750195</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.5884763083053528</v>
+        <v>-0.5152191985256565</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-1.438395104635212</v>
+        <v>-1.339047779340639</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>2.558584409373509</v>
+        <v>2.658492445392184</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>3.433298696182611</v>
+        <v>3.556995317210855</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-1.188532829399705</v>
+        <v>-1.039843281621877</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.1224610447193939</v>
+        <v>0.04953771484726843</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; 110.8</t>
+          <t>X &gt; 110.7</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>102</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.4602604400538866</v>
+        <v>0.4310646457012552</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>4.731427288166529</v>
+        <v>4.730240501721873</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>4.33665590341149</v>
+        <v>4.336502513407169</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>4.466881046999852</v>
+        <v>4.466386554621849</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.9733692904095719</v>
+        <v>-0.9248233706438</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>2.265181209813747</v>
+        <v>2.28913861876336</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>1.200078693684837</v>
+        <v>1.248090372675158</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-1.227774263827392</v>
+        <v>-1.178526701433675</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>1.652420050238064</v>
+        <v>1.72567716001776</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.8025012539082041</v>
+        <v>0.9018485792027775</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>4.519368723098992</v>
+        <v>4.619276759117668</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>5.534139032317064</v>
+        <v>5.657835653345309</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>0.212027394689926</v>
+        <v>0.3607169424677537</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>1.418155201779214</v>
+        <v>1.590153961345877</v>
       </c>
     </row>
     <row r="35">
@@ -3725,46 +3725,46 @@
         <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>2.280988731370414</v>
+        <v>2.251792937017782</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>9.003135971639914</v>
+        <v>9.001949185195258</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>9.798840777361072</v>
+        <v>9.79868738735675</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>9.929065920949434</v>
+        <v>9.928571428571431</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>4.628871605948973</v>
+        <v>4.677417525714745</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>7.307198016536439</v>
+        <v>7.331155425486052</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>8.412963847746461</v>
+        <v>8.460975526736782</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>4.374466632531153</v>
+        <v>4.42371419492487</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>7.884913047436946</v>
+        <v>7.958170157216642</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>7.034994251107086</v>
+        <v>7.13434157640166</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>12.78267404522785</v>
+        <v>12.88258208124653</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>16.38848076901174</v>
+        <v>16.51217739003999</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>11.20642515379357</v>
+        <v>11.3551147015714</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>12.6226369944963</v>
+        <v>12.79463575406296</v>
       </c>
     </row>
   </sheetData>
@@ -3911,46 +3911,46 @@
         <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>9.423845874227553</v>
+        <v>9.394650079874921</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>9.003135971639914</v>
+        <v>9.001949185195258</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>13.37026934878964</v>
+        <v>13.37011595878532</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>13.500494492378</v>
+        <v>13.5</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>12.96220493928231</v>
+        <v>13.01075085904808</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>16.83100754034596</v>
+        <v>16.85496494929558</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>16.7462971810798</v>
+        <v>16.79430886007012</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>19.85065710872163</v>
+        <v>19.89990467111534</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>18.59919876172266</v>
+        <v>18.67245587150236</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>22.51118472729756</v>
+        <v>22.61053205259213</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>21.11600737856118</v>
+        <v>21.21591541457985</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>23.5313379118689</v>
+        <v>23.65503453289714</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>25.49213943950785</v>
+        <v>25.64082898728568</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>25.71787508973438</v>
+        <v>25.88987384930105</v>
       </c>
     </row>
     <row r="7">
@@ -3963,46 +3963,46 @@
         <v>221</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>5.890124693447554</v>
+        <v>5.860928899094922</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>8.80382547821177</v>
+        <v>8.802638691767115</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>13.8389183468504</v>
+        <v>13.83876495684608</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>11.70670005152473</v>
+        <v>11.70620555914672</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>12.07338787399464</v>
+        <v>12.12193379376041</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>11.46578452806412</v>
+        <v>11.48974193701373</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>15.0009836710604</v>
+        <v>15.04899535005072</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>16.34386977840489</v>
+        <v>16.3931173407986</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>15.83039893409931</v>
+        <v>15.903656043879</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>16.33794620111786</v>
+        <v>16.43729352641243</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>14.77577897950925</v>
+        <v>14.87568701552793</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>14.35766844408177</v>
+        <v>14.48136506511002</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>14.84249496633397</v>
+        <v>14.9911845141118</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>15.06823061656051</v>
+        <v>15.24022937612717</v>
       </c>
     </row>
     <row r="8">
@@ -4015,150 +4015,150 @@
         <v>426</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>4.561337490592408</v>
+        <v>4.532141696239776</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>4.593343885791491</v>
+        <v>4.592157099346835</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>6.545990341412043</v>
+        <v>6.545836951407722</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>5.502506564812606</v>
+        <v>5.502012072434603</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>5.903184147867144</v>
+        <v>5.951730067632916</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>5.965816393464671</v>
+        <v>5.989773802414284</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>7.759040306498981</v>
+        <v>7.807051985489302</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>7.291971662712243</v>
+        <v>7.341219225105959</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>7.230989506189466</v>
+        <v>7.304246615969163</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>7.789521414084952</v>
+        <v>7.888868739379525</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>6.645853119674527</v>
+        <v>6.745761155693202</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>7.14971484010497</v>
+        <v>7.273411461133215</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>7.903272906979353</v>
+        <v>8.051962454757181</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>8.598492125280991</v>
+        <v>8.770490884847653</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; 28.04</t>
+          <t>X &lt; 28.05</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>626</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>4.068604736238811</v>
+        <v>4.03940894188618</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>3.415885096849109</v>
+        <v>3.414698310404454</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>3.979580165768191</v>
+        <v>3.979426775763869</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>3.151338855682432</v>
+        <v>3.150844363304429</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>3.252026938369482</v>
+        <v>3.300572858135254</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>3.549400968004569</v>
+        <v>3.573358376954182</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>4.423157062412521</v>
+        <v>4.471168741402842</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>3.476855191788722</v>
+        <v>3.526102754182439</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>3.895106262103006</v>
+        <v>3.968363371882702</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>3.684165101555891</v>
+        <v>3.783512426850464</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>3.000230716458638</v>
+        <v>3.100138752477314</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>2.555375641976902</v>
+        <v>2.679072263005146</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>3.093691242337613</v>
+        <v>3.24238079011544</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>4.118148937292588</v>
+        <v>4.29014769685925</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; 31.35</t>
+          <t>X &lt; 31.36</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>865</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>3.58844813131536</v>
+        <v>3.559252336962729</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>3.364545275245746</v>
+        <v>3.36335848880109</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>3.432201636155447</v>
+        <v>3.432048246151126</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>3.79364065257618</v>
+        <v>3.793146160198177</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>3.370958035896678</v>
+        <v>3.419503955662449</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>3.552725129115572</v>
+        <v>3.576682538065185</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>5.317725752508366</v>
+        <v>5.365737431498687</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>5.197477917970183</v>
+        <v>5.246725480363899</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>5.483316570695962</v>
+        <v>5.556573680475658</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>5.211432456447028</v>
+        <v>5.310779781741601</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>4.42869661610591</v>
+        <v>4.528604652124585</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>4.694288641293596</v>
+        <v>4.817985262321841</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>5.430207152142039</v>
+        <v>5.578896699919866</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>6.002763611617134</v>
+        <v>6.174762371183796</v>
       </c>
     </row>
     <row r="11">
@@ -4168,49 +4168,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>2.36071292874167</v>
+        <v>2.453787092080532</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>1.83549968635657</v>
+        <v>1.913937828891221</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>1.802719251827774</v>
+        <v>1.84208702569309</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>2.656926295868622</v>
+        <v>2.656431803490619</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>2.480627692999171</v>
+        <v>2.529173612764943</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>2.687503985077697</v>
+        <v>2.71146139402731</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>4.503246114499319</v>
+        <v>4.55125779348964</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>4.217172945825702</v>
+        <v>4.266420508219419</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>4.789674952198851</v>
+        <v>4.862932061978547</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>4.573240318764917</v>
+        <v>4.67258764405949</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>3.916050472721921</v>
+        <v>4.015958508740596</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>4.548418657210497</v>
+        <v>4.617111671444853</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>4.85290548505651</v>
+        <v>4.94593564533352</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>5.078641135283043</v>
+        <v>5.104482769792327</v>
       </c>
     </row>
     <row r="12">
@@ -4220,49 +4220,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1387</v>
+        <v>1398</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>1.376226826608509</v>
+        <v>1.423268756261145</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>1.447569070111612</v>
+        <v>1.438625983574184</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>1.736302457312021</v>
+        <v>1.72305117119533</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>2.622592866444876</v>
+        <v>2.603084415584412</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>2.125119388729701</v>
+        <v>2.012172323156115</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>2.893475538297828</v>
+        <v>2.823264075489433</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>3.423895049495457</v>
+        <v>3.301680491996905</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>3.28568941310067</v>
+        <v>3.1620129332236</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>3.554042768290806</v>
+        <v>3.380394642163864</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>3.896621720211193</v>
+        <v>3.668204765043733</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>3.303400321349812</v>
+        <v>3.078360606789502</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>4.100606656083627</v>
+        <v>3.821701199563798</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>4.300290942183857</v>
+        <v>3.969737391247698</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>5.002559403257919</v>
+        <v>4.61969195680156</v>
       </c>
     </row>
     <row r="13">
@@ -4272,49 +4272,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1730</v>
+        <v>1741</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.07215339000494936</v>
+        <v>0.1124651420457354</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.2132939728426919</v>
+        <v>0.2136135428949828</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.07946767487480599</v>
+        <v>0.07918314730456188</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.2985240490282521</v>
+        <v>0.2973402953414279</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.2516980798392723</v>
+        <v>0.1821794304766442</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.7534142475628016</v>
+        <v>0.7151299415360342</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>1.161133927522762</v>
+        <v>1.086561230125696</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.8990442054958123</v>
+        <v>0.8243465715160312</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.928003482458216</v>
+        <v>0.8194039978319267</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.7448311270339261</v>
+        <v>0.6007080656907888</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.2266880039561769</v>
+        <v>0.08496303362747426</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>1.101996660356733</v>
+        <v>0.9212422207915623</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>1.292667623051635</v>
+        <v>1.075468974164473</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>2.129931241674932</v>
+        <v>1.874529630051036</v>
       </c>
     </row>
     <row r="14">
@@ -4324,49 +4324,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2006</v>
+        <v>2017</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.02032220621651959</v>
+        <v>0.05146452979282401</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.2686510974127216</v>
+        <v>0.2684656488531658</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.0495667494554084</v>
+        <v>0.04946225351622502</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.04117217428866837</v>
+        <v>-0.04041863415321956</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.1058560320044677</v>
+        <v>-0.1573495499210367</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.3180269757268661</v>
+        <v>0.2905910515883505</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>1.005753571683719</v>
+        <v>0.9487413840678514</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.715468241922423</v>
+        <v>0.6586787689897875</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.6325391988423164</v>
+        <v>0.5503702419983227</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.5069203349734721</v>
+        <v>0.3973419769577333</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.01805600288896159</v>
+        <v>-0.1254330059764825</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.8411462973744861</v>
+        <v>0.7034319007595755</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>1.19681592893771</v>
+        <v>1.030181953447375</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>1.80034197479349</v>
+        <v>1.605221961773609</v>
       </c>
     </row>
     <row r="15">
@@ -4376,49 +4376,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2271</v>
+        <v>2282</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.05848852288070816</v>
+        <v>0.08248076770560431</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.1347923135459297</v>
+        <v>0.1351330603146152</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.1581746949771983</v>
+        <v>0.1575435333912552</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.268516036813395</v>
+        <v>0.2676389927698821</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.368219976876297</v>
+        <v>0.3260217950086641</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.6459639748723873</v>
+        <v>0.6229000709424852</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>1.068384224852529</v>
+        <v>1.023229786238744</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>1.021056757382148</v>
+        <v>0.9750794962901637</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.896880576100429</v>
+        <v>0.8314497707673496</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.8628330789459113</v>
+        <v>0.7757613989238479</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.2873856924197042</v>
+        <v>0.2025779132773593</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.7865910910111893</v>
+        <v>0.6794695258084857</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.8756907473549376</v>
+        <v>0.7472053091679172</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>1.56709192309917</v>
+        <v>1.415728362885623</v>
       </c>
     </row>
     <row r="16">
@@ -4428,49 +4428,49 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2484</v>
+        <v>2495</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.09805659921676835</v>
+        <v>-0.0778949189858622</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.1546927481966875</v>
+        <v>0.154816395102749</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.1381761135636381</v>
+        <v>-0.1374658448858668</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.2668328074272495</v>
+        <v>-0.2653264898773955</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.2619655953575517</v>
+        <v>-0.2936763431426996</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.1834386875834184</v>
+        <v>-0.1988561796354276</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.1952849656757678</v>
+        <v>0.161900501043057</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.1920225705690157</v>
+        <v>0.1578015123788461</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.007432319797935349</v>
+        <v>-0.05706793802145427</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.1518837155136481</v>
+        <v>-0.2185996000689272</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.4949409814824719</v>
+        <v>-0.560553379503034</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.4783544606553463</v>
+        <v>-0.5602142418230116</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.5943796751802708</v>
+        <v>-0.6927332837765903</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.06427351850118157</v>
+        <v>-0.1808390049789423</v>
       </c>
     </row>
     <row r="17">
@@ -4480,49 +4480,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2703</v>
+        <v>2714</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.1613284016683707</v>
+        <v>-0.1448753012346131</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.4567008229948186</v>
+        <v>0.4555005250268636</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.1557204489054342</v>
+        <v>0.1551749365048423</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.1217887896767138</v>
+        <v>0.1215649255296825</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.02768128069241271</v>
+        <v>-0.05388373514949762</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.005162560302188979</v>
+        <v>-0.01813256303778843</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.1516740919917652</v>
+        <v>0.1250171080881728</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.3692986738748232</v>
+        <v>0.3410811417035831</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.2549629876493711</v>
+        <v>0.2141641325927424</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.2751828274611654</v>
+        <v>0.2201189337021958</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.09347419677404645</v>
+        <v>-0.147370422390189</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.1834812091138431</v>
+        <v>0.115515632553489</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.08005152741993982</v>
+        <v>-0.001107345258390069</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.2157874622305513</v>
+        <v>0.1213719017276205</v>
       </c>
     </row>
     <row r="18">
@@ -4532,49 +4532,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2945</v>
+        <v>2956</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.04683895142684236</v>
+        <v>-0.03453082118203099</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.45642679084213</v>
+        <v>0.4552286101727958</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.2830858962475915</v>
+        <v>0.2821001660172513</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.2111322903147723</v>
+        <v>-0.210143531451692</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.2571586355315034</v>
+        <v>-0.2764088615011886</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.2460569461326827</v>
+        <v>-0.2551179502610097</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.07522817703092954</v>
+        <v>-0.09494430997953884</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.1878309480981102</v>
+        <v>0.166616352411765</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.0778105454191973</v>
+        <v>0.04699150135713381</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.09438484355973742</v>
+        <v>0.0526169946770807</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.3626383538158962</v>
+        <v>-0.4029551819859094</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.003895658994146345</v>
+        <v>-0.05548415733758105</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.1673504256846527</v>
+        <v>-0.2287782401166112</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.05825879336044437</v>
+        <v>-0.1298439160188778</v>
       </c>
     </row>
     <row r="19">
@@ -4584,49 +4584,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3120</v>
+        <v>3131</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.1030034866466991</v>
+        <v>-0.09280902590479201</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.03718513764670917</v>
+        <v>-0.03665512066962862</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.3508147411861842</v>
+        <v>-0.34953485507301</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.8742202497488805</v>
+        <v>-0.8709919497885181</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.9479900111810977</v>
+        <v>-0.9610416796234418</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-1.017001228378923</v>
+        <v>-1.02151982747592</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-1.020617707677118</v>
+        <v>-1.033242810693793</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.7027657959488778</v>
+        <v>-0.7169266964332692</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.9383250478011504</v>
+        <v>-0.9597720196541033</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.746543460008084</v>
+        <v>-0.7774834406865097</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-1.125655857338359</v>
+        <v>-1.155464534974946</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.7533086821947492</v>
+        <v>-0.792475080587586</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.6750688728462393</v>
+        <v>-0.7229732385855101</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.5916487197894185</v>
+        <v>-0.6477453504069359</v>
       </c>
     </row>
     <row r="20">
@@ -4636,101 +4636,101 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3210</v>
+        <v>3221</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.04778393843864848</v>
+        <v>0.05636931302272075</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.1909518801262138</v>
+        <v>0.1906578885961991</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.2180129060557974</v>
+        <v>-0.2172249181595234</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.6299402902306994</v>
+        <v>-0.6276473449175413</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.7166216705787889</v>
+        <v>-0.7287449392712517</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.775314043601476</v>
+        <v>-0.7798622860271678</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.7811241076097559</v>
+        <v>-0.7928747122435666</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.3607856773480265</v>
+        <v>-0.3743438569292792</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.5602472873034898</v>
+        <v>-0.5803413416172347</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.4597460221023795</v>
+        <v>-0.4880283017821725</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.8650072495122743</v>
+        <v>-0.8920841127745121</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.4709155424393643</v>
+        <v>-0.5064979050858227</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.4999858441154075</v>
+        <v>-0.5429964982157713</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.5059789378579538</v>
+        <v>-0.5559947806718952</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 67.75</t>
+          <t>X &lt; 67.74</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3325</v>
+        <v>3336</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.09547701919602503</v>
+        <v>0.1026083901025672</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.08829943468770551</v>
+        <v>0.08831204575167106</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.2302787841326008</v>
+        <v>-0.2294828290417286</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.683484946473996</v>
+        <v>-0.6811117752540383</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.6657837486943805</v>
+        <v>-0.6759884106508309</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.8321873505717008</v>
+        <v>-0.8355682017638983</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.7206896136380934</v>
+        <v>-0.7305832385581468</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.3009490155653722</v>
+        <v>-0.3125429650306799</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.645760483236586</v>
+        <v>-0.6623597668152286</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.6081561301027634</v>
+        <v>-0.6315552014711727</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-1.186820002391201</v>
+        <v>-1.208463141874169</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.8052587646736882</v>
+        <v>-0.8342518946756954</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.7878193269211451</v>
+        <v>-0.8232747842798815</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.8460346847017064</v>
+        <v>-0.8872758595033332</v>
       </c>
     </row>
     <row r="22">
@@ -4740,49 +4740,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3494</v>
+        <v>3505</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.01442045026631433</v>
+        <v>-0.008690562806258129</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.01337993306766805</v>
+        <v>-0.01310693677015706</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.05035425015065442</v>
+        <v>-0.05016683009815637</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.3041369492397408</v>
+        <v>-0.303088803088805</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.4273387171754308</v>
+        <v>-0.4354642803941502</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.48562785167492</v>
+        <v>-0.4887786967537906</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.4691922709135099</v>
+        <v>-0.4770871698680494</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.09220003413551581</v>
+        <v>-0.1015194245838842</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.5947205893844583</v>
+        <v>-0.6071534081069245</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.714331894445472</v>
+        <v>-0.7314864304921826</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-1.017590126783531</v>
+        <v>-1.033908118025892</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.6241595273814156</v>
+        <v>-0.6463626726916942</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.4275417376840451</v>
+        <v>-0.455251201777962</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.5291606449945334</v>
+        <v>-0.5611145346402608</v>
       </c>
     </row>
     <row r="23">
@@ -4792,49 +4792,49 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3615</v>
+        <v>3626</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.08290059503269731</v>
+        <v>-0.07812501532391281</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.2183772821314065</v>
+        <v>-0.2175330002022662</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.2949264592633156</v>
+        <v>-0.2940106761964216</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.4532000889027969</v>
+        <v>-0.4517523180889498</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.5351145183020591</v>
+        <v>-0.5410274864028892</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.5815550557661808</v>
+        <v>-0.5835129184613166</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.5409158819477327</v>
+        <v>-0.5467316023576316</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.2197654264896372</v>
+        <v>-0.2267473112635088</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.4865681417238008</v>
+        <v>-0.4964730605772232</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.6581990803841151</v>
+        <v>-0.6716403204893311</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.9581456657411209</v>
+        <v>-0.9707685728756985</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.6320045055514996</v>
+        <v>-0.6493178585555981</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.3730628360926573</v>
+        <v>-0.3950526937572931</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.380722025460237</v>
+        <v>-0.4063203040359582</v>
       </c>
     </row>
     <row r="24">
@@ -4844,49 +4844,49 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3680</v>
+        <v>3691</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.1115686165078174</v>
+        <v>-0.1073040495090183</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.3001194583760736</v>
+        <v>-0.2990680080714583</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.4093877321408144</v>
+        <v>-0.4081506152673171</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.5626104243854542</v>
+        <v>-0.5608715791099002</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.6797034369714225</v>
+        <v>-0.6842298359326193</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.7201235411538818</v>
+        <v>-0.7212139407519231</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.6274871577167502</v>
+        <v>-0.6320992369707525</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.2388708348486333</v>
+        <v>-0.2448072574754079</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.4749112079096918</v>
+        <v>-0.4833882843417996</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.6042177854990811</v>
+        <v>-0.6158356257376525</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.902468760197344</v>
+        <v>-0.9132773561938592</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.6900997126105679</v>
+        <v>-0.7047581250271264</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.4431654077774283</v>
+        <v>-0.4619414816819685</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.3923733574705821</v>
+        <v>-0.4144571488798547</v>
       </c>
     </row>
     <row r="25">
@@ -4896,49 +4896,49 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3776</v>
+        <v>3787</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.1715995882012891</v>
+        <v>-0.1680065617290936</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.237825460451397</v>
+        <v>-0.2370109421565445</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.327908628501099</v>
+        <v>-0.3269426434865537</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.4210963309560967</v>
+        <v>-0.419823921140754</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.4695746417707198</v>
+        <v>-0.4733677620568457</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.5277964463650022</v>
+        <v>-0.528810695349641</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.5453458837591469</v>
+        <v>-0.5488645716641969</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.2841921773703859</v>
+        <v>-0.2886004699339608</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.330663582580307</v>
+        <v>-0.3374898789497252</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.451778235665401</v>
+        <v>-0.4610284101579865</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.6682262937381225</v>
+        <v>-0.6769103172960058</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.5661941660761158</v>
+        <v>-0.5777068613644545</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.2302782010988267</v>
+        <v>-0.245428366764699</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.2544312056651279</v>
+        <v>-0.2719957044354118</v>
       </c>
     </row>
     <row r="26">
@@ -4948,101 +4948,101 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3843</v>
+        <v>3854</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0.03464413544075029</v>
+        <v>0.03708238250892748</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.084320022430866</v>
+        <v>-0.08397695970656827</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.1277660874917785</v>
+        <v>-0.127389123454563</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.1651093042924998</v>
+        <v>-0.1645962732919273</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.1960801816196422</v>
+        <v>-0.1997443149469689</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.2220770017024805</v>
+        <v>-0.223528799317279</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.2666898319072146</v>
+        <v>-0.270108204346954</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.07010152988579677</v>
+        <v>-0.07418859313336412</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.142757480233584</v>
+        <v>-0.1487289901074789</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.1725391391661049</v>
+        <v>-0.180699525575676</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.388709952989224</v>
+        <v>-0.3963047911067719</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.2617762128447225</v>
+        <v>-0.2718079883437312</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.04301739117447312</v>
+        <v>-0.05585435531205718</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>0.04132031481896092</v>
+        <v>0.02620715792288308</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 87.6</t>
+          <t>X &lt; 87.59</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3881</v>
+        <v>3892</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.1128179191317997</v>
+        <v>0.1147281238966258</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.03068236137485059</v>
+        <v>0.03068649979322657</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.04185809211477931</v>
+        <v>-0.04172841001524574</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.05184240228734893</v>
+        <v>-0.0516584901515742</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.03632609266774978</v>
+        <v>-0.03993211601326863</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.03340857837716982</v>
+        <v>-0.03514494081431963</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.1040849470801035</v>
+        <v>-0.1074608244643755</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>0.1117839417548154</v>
+        <v>0.1077035423313504</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0.09075575508099121</v>
+        <v>0.08489767655386515</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.07875229486513291</v>
+        <v>0.07093099656397328</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.1887349097032498</v>
+        <v>-0.1958456955124532</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-0.1141620084185675</v>
+        <v>-0.1233057708668994</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>0.1241406171040822</v>
+        <v>0.1124080119086415</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>0.1326061973281654</v>
+        <v>0.1190619274099944</v>
       </c>
     </row>
     <row r="28">
@@ -5052,49 +5052,49 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3910</v>
+        <v>3921</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.05540821111744521</v>
+        <v>0.05724963927163174</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.01255087423561463</v>
+        <v>-0.01243460035556865</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.08748559710608816</v>
+        <v>-0.08723035715713223</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.09644428313220033</v>
+        <v>-0.09614056764909407</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.01702942074622626</v>
+        <v>0.01365889249046148</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.003383183784421817</v>
+        <v>-0.005013962095901547</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.04862604733845899</v>
+        <v>-0.05177784345039527</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>0.1111269759330611</v>
+        <v>0.107442231594078</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0.03871709779272692</v>
+        <v>0.03358921939067727</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.02049197600184272</v>
+        <v>0.01362577415719812</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.1954331189258269</v>
+        <v>-0.2017342140789538</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.1978470136350623</v>
+        <v>-0.2057741290841051</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>0.009982884735599384</v>
+        <v>-0.0002433518998614659</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>0.02003073460102911</v>
+        <v>0.008174574334752549</v>
       </c>
     </row>
     <row r="29">
@@ -5104,49 +5104,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3932</v>
+        <v>3943</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.04126394411711232</v>
+        <v>0.04297209826771109</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.009952022178303821</v>
+        <v>-0.009850224834238475</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.01058641730579524</v>
+        <v>-0.01054738394176269</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.006619012201149133</v>
+        <v>0.006631491453141791</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.1418547743495466</v>
+        <v>0.1384258156704021</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.003655258783844317</v>
+        <v>-0.005142799194857162</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0.001655683963058152</v>
+        <v>-0.001351176096257234</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>0.1325260777414385</v>
+        <v>0.1290766133792118</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0.06018549321993305</v>
+        <v>0.05543459490661462</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.08813013960883609</v>
+        <v>0.08166745380101759</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.1023020544877724</v>
+        <v>-0.1082706207060298</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.129905945104511</v>
+        <v>-0.137288479958201</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.001849155167235494</v>
+        <v>-0.01115594461811042</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.06689456583892905</v>
+        <v>-0.07748240590709088</v>
       </c>
     </row>
     <row r="30">
@@ -5156,49 +5156,49 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3959</v>
+        <v>3970</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.0367073330104688</v>
+        <v>0.03821857933093753</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.02511647766516489</v>
+        <v>-0.02498152681832266</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.003246304322992444</v>
+        <v>-0.003228857664240081</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.03566071044387087</v>
+        <v>-0.03553481694185479</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.06977982407493499</v>
+        <v>0.06690279959308043</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.04752607627689542</v>
+        <v>-0.04871960144780019</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>0.007589595170998109</v>
+        <v>0.004912689230643252</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>0.08394840758669631</v>
+        <v>0.08099119023002999</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0.06212702081641197</v>
+        <v>0.05790061543766711</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.05885784650740078</v>
+        <v>0.05319507653346989</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.03071986357241485</v>
+        <v>-0.03616709473899959</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.03263703433277243</v>
+        <v>-0.03939792286463728</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>0.1169590643274816</v>
+        <v>0.1083974299233788</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>0.05392676223465287</v>
+        <v>0.0442459255874823</v>
       </c>
     </row>
     <row r="31">
@@ -5208,49 +5208,49 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3984</v>
+        <v>3995</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.05848852288070816</v>
+        <v>0.05974845455413202</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.03804806954412498</v>
+        <v>-0.03788586537101679</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.0438196910816302</v>
+        <v>-0.04369190085379415</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.02515111889606203</v>
+        <v>-0.0250579632602097</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.1513931615283823</v>
+        <v>0.1486129969102095</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.06175474904907929</v>
+        <v>0.0604180023629155</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>0.1160219188827014</v>
+        <v>0.1133636184052378</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>0.1890029733832819</v>
+        <v>0.1860831265014937</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0.1669624929358804</v>
+        <v>0.1629320619785517</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>0.158412123772699</v>
+        <v>0.1531319882903404</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>0.01797448594589213</v>
+        <v>0.01305207814973386</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>0.04138498137405833</v>
+        <v>0.03523635092731325</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>0.1874253330371616</v>
+        <v>0.1796535261102221</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>0.1262227661543562</v>
+        <v>0.117479785292474</v>
       </c>
     </row>
     <row r="32">
@@ -5260,49 +5260,49 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4005</v>
+        <v>4016</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.03277237165578839</v>
+        <v>0.03394377203532883</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.02788791872195873</v>
+        <v>0.02786302640205207</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.02009860320056589</v>
+        <v>0.02005033034869541</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.03936657919528841</v>
+        <v>0.03928039173940334</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.2370999496033264</v>
+        <v>0.2343533435201337</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.1495081277227044</v>
+        <v>0.1480635008434277</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.1781444962770564</v>
+        <v>0.1755808319461067</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>0.1984506764104808</v>
+        <v>0.1957773712645263</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0.2260839297549566</v>
+        <v>0.2222954044306746</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.2131410398799716</v>
+        <v>0.2082577100192893</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>0.07238034691019379</v>
+        <v>0.06785678829280783</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.0709055732234134</v>
+        <v>0.06535475854836648</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.2139852422323401</v>
+        <v>0.2069586505027203</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0.1542938519958454</v>
+        <v>0.1464190968821555</v>
       </c>
     </row>
     <row r="33">
@@ -5312,101 +5312,101 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4030</v>
+        <v>4041</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.02959596550818588</v>
+        <v>0.03058871778691952</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.05944502315285405</v>
+        <v>-0.05924005734113535</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.04490369890011436</v>
+        <v>-0.04477615798241885</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.0002127212004978674</v>
+        <v>-0.0001939556370658124</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.168196521357082</v>
+        <v>0.1659536809175606</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.1572652351029191</v>
+        <v>0.1559563757500868</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.2099724703681574</v>
+        <v>0.2076346647002723</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>0.2272676141725682</v>
+        <v>0.2248367195462819</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0.2295758196090176</v>
+        <v>0.2262538612865086</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>0.2362360765432641</v>
+        <v>0.2319341362933542</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>0.09508475213396395</v>
+        <v>0.09114503164923349</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.09383791186888857</v>
+        <v>0.08902390900868795</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>0.2334301507811958</v>
+        <v>0.2273137543741157</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>0.1755142247928845</v>
+        <v>0.1686945089680378</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; 110.8</t>
+          <t>X &lt; 110.7</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4047</v>
+        <v>4058</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.0313992404016048</v>
+        <v>0.03226105646895405</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.0640163881953697</v>
+        <v>-0.06380488055880562</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.1004762683335088</v>
+        <v>-0.1001996680798314</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.08008933099606708</v>
+        <v>-0.0798567214496444</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.06068338391459349</v>
+        <v>0.05894363013241133</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.05101810930844408</v>
+        <v>0.0501023254462325</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.1277898866968172</v>
+        <v>0.1258850329747006</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>0.1677062081541436</v>
+        <v>0.1656527026114105</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.1697341822087211</v>
+        <v>0.1668946511983407</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.1727850376265749</v>
+        <v>0.1690887101148135</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.0560426519297863</v>
+        <v>0.05264340791951838</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.05493574319701366</v>
+        <v>0.05076523897265872</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>0.1921676721447838</v>
+        <v>0.1868114600974238</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>0.1354330691900714</v>
+        <v>0.1294711174838241</v>
       </c>
     </row>
     <row r="35">
@@ -5416,49 +5416,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4065</v>
+        <v>4076</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.004211763736904572</v>
+        <v>-0.003386464163092739</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.1308561093720328</v>
+        <v>-0.1304709061289415</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.1934485819547973</v>
+        <v>-0.1929236441368403</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.1725992850102571</v>
+        <v>-0.1721208307111439</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.05939545345210462</v>
+        <v>-0.06059028450849269</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.04318136919771831</v>
+        <v>-0.04373380542668315</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.01626245967237594</v>
+        <v>-0.0175591641417796</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>0.04594082279678702</v>
+        <v>0.04444166278609174</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0.04766021018410527</v>
+        <v>0.04548535773938767</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0.04690779017717261</v>
+        <v>0.04400544194788125</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.09483684113259727</v>
+        <v>-0.09737332332275628</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.1450000932126656</v>
+        <v>-0.1480668940395091</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.03487904127354113</v>
+        <v>-0.03894255341301545</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.09041870748929171</v>
+        <v>-0.09498525626463561</v>
       </c>
     </row>
   </sheetData>
